--- a/docs/Nyaymalaw_Implementation_Plan.xlsx
+++ b/docs/Nyaymalaw_Implementation_Plan.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Plan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Implementation Plan'!$A$1:$O$16</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Implementation Plan'!$A$1:$P$28</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -225,35 +225,40 @@
     </comment>
     <comment ref="I1" authorId="0" shapeId="0">
       <text>
-        <t>How it is tested: the scenario and what is checked.</t>
+        <t>Must do and Must never written as the scenarios that test them. The test files in tests/features/ are generated from this column: edit here, never there.</t>
       </text>
     </comment>
     <comment ref="J1" authorId="0" shapeId="0">
       <text>
-        <t>Offline test / Corpus / Model-judged / Human expert.</t>
+        <t>How it is tested: the scenario and what is checked.</t>
       </text>
     </comment>
     <comment ref="K1" authorId="0" shapeId="0">
       <text>
-        <t>The threshold that counts as a pass, e.g. 3/3 scenarios.</t>
+        <t>Offline test / Corpus / Model-judged / Human expert.</t>
       </text>
     </comment>
     <comment ref="L1" authorId="0" shapeId="0">
       <text>
-        <t>Pilot / Production / Later.</t>
+        <t>The threshold that counts as a pass, e.g. 3/3 scenarios.</t>
       </text>
     </comment>
     <comment ref="M1" authorId="0" shapeId="0">
       <text>
-        <t>Not started / Built / Built + eval passing.</t>
+        <t>Pilot / Production / Later.</t>
       </text>
     </comment>
     <comment ref="N1" authorId="0" shapeId="0">
       <text>
+        <t>Not started / Built / Built + eval passing.</t>
+      </text>
+    </comment>
+    <comment ref="O1" authorId="0" shapeId="0">
+      <text>
         <t>Pass / Fail / Not run, with the date and a link to the run. Never typed without a run.</t>
       </text>
     </comment>
-    <comment ref="O1" authorId="0" shapeId="0">
+    <comment ref="P1" authorId="0" shapeId="0">
       <text>
         <t>Anything stopping this row.</t>
       </text>
@@ -551,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O16"/>
+  <dimension ref="A1:P28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -562,13 +567,14 @@
     <col width="36" customWidth="1" min="6" max="6"/>
     <col width="44" customWidth="1" min="7" max="7"/>
     <col width="44" customWidth="1" min="8" max="8"/>
-    <col width="48" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="30" customWidth="1" min="11" max="11"/>
-    <col width="13" customWidth="1" min="12" max="12"/>
-    <col width="18" customWidth="1" min="13" max="13"/>
-    <col width="44" customWidth="1" min="14" max="14"/>
-    <col width="40" customWidth="1" min="15" max="15"/>
+    <col width="70" customWidth="1" min="9" max="9"/>
+    <col width="48" customWidth="1" min="10" max="10"/>
+    <col width="16" customWidth="1" min="11" max="11"/>
+    <col width="30" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="18" customWidth="1" min="14" max="14"/>
+    <col width="44" customWidth="1" min="15" max="15"/>
+    <col width="40" customWidth="1" min="16" max="16"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1">
@@ -614,35 +620,40 @@
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
+          <t>Scenarios (Given / When / Then)</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
           <t>Eval</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Eval type</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Pass bar</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Release</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Build status</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Result and evidence</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="P1" s="1" t="inlineStr">
         <is>
           <t>Blocker / notes</t>
         </is>
@@ -673,7 +684,29 @@
 3. Remove recovery codes throughout the application.
 4. Remove the logo from the other cards too; there should be only one logo on the page at any point in time — in this case we already have it on the left side of the page.
 5. Forgot password: yes, an email reset link.
-Follow-up (15 September 2026): send the email to the registered email. Record this and keep it as pending; we will pick it up in future.</t>
+Follow-up (15 September 2026): send the email to the registered email. Record this and keep it as pending; we will pick it up in future.
+Follow-up 2 (15 September 2026):
+• Keep the Given/When/Then scenarios in this implementation plan sheet, in their own column, instead of separate files.
+• Forgot password promise: agreed. Send either a link or a code to the registered email; it is in the plan and we will implement it. Once that is done, anyone registering with someone else's email goes away.
+• Register and login use only email. Once a person is logged in, a profile page inside the application will capture details like advocate ID, mobile number and so on. Keep this in the back of your mind; we will build it in the profile page.
+• Privacy notice and consent at registration: we should absolutely do that. Prepare a note based on your understanding of India's data protection laws.
+• Show password button on the sign-in card: absolutely add this.
+• Two-step sign-in: park it for now; we will come back to it later.
+• Session length: make it three hours. After three hours the advocate should log in again.
+• Advocates will sign in from desktop, phones and tablets, so be prepared for all three views.
+• Add all the above features to the implementation plan under the Arrive phase.
+Follow-up 3 (15 September 2026), answers to six questions:
+1. Link or code for the email: use haaruln@gmail.com to send mails through Gmail.
+2. Confirm the email before the account works: yes.
+3. Email or advocate ID: let both work.
+4. Session: make it 30 min of inactivity, meaning there is no activity — no typing, moving cursor, opening some tabs — none of that; the app/website window was not touched at all for 30 mins — then sign out. When there is activity, the clock lapses and resets at the beginning of the next inactivity.
+5. Widths for desktop, tablet and phone: ok.
+6. The rows for withdrawing consent and for my data and grievances: yes. Privacy contact: haaruln@gmail.com. Nyaymalaw signs the contract through Rahul Lambade, Founder &amp; CEO.
+Stage 2 — Top ribbon and home page (15 September 2026).
+For all the pages across Nyaymalaw, this ribbon should be constant and frozen across all the pages. The way it is today, we should have the NM logo, then Nyaymalaw. Below that, let us have the Home tab, then My work, then Legal library — replace Research with Library, or just call it Legal library — then keep Preparation also. So only these four tabs: Home, My work, Legal library, Preparation, below NM. And this should remain across the pages.
+On the right side, aligned to Nyaymalaw in the first row the way it is today, just put the user name, which is Lambade Rahul, and Active workspace — Lambade Rahul's private workspace — that you can keep. After Lambade Rahul, put a person's icon with an arrow button; if you click on it, it should show a pop-up or a small drop-down which shows Profile — the profile should have all the profile details — and also put Sign out. This is the top ribbon, which should be there across the pages throughout Nyaymalaw.
+Then the home page. The home page should be very clean. It should have just one to two lines of introduction — what NM is — and below that a button to start a matter. Do this for now.
+Stage 2 decisions (15 September 2026): keep the 12 hour limit, go with your ribbon proposals.</t>
         </is>
       </c>
       <c r="D2" s="4" t="n"/>
@@ -688,6 +721,7 @@
       <c r="M2" s="4" t="n"/>
       <c r="N2" s="4" t="n"/>
       <c r="O2" s="4" t="n"/>
+      <c r="P2" s="4" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
@@ -728,35 +762,59 @@
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
-          <t>Page/script contract: card content, link order and row, no text below (tests/test_the_page_and_the_script_agree.py, with a planted-failure control). Served sign-in: right password, wrong password, unknown and unreadable account (tests/test_public_email_registration.py). Screenshot of the card.</t>
+          <t xml:space="preserve">  Scenario: The sign-in card shows only its own content
+    Given the sign-in page
+    Then the sign-in card shows "Welcome back." and "Sign in to your practice workspace."
+    And the sign-in card has an email field, a password field and a Sign in button
+    And the sign-in card carries no logo and no text below its links
+  Scenario: Forgot password and Register sit in one row under Sign in
+    Given the sign-in page
+    Then directly under the Sign in button there is one row as wide as the button
+    And the row shows Forgot password on the left and Register on the right
+  Scenario: A correct email and password opens the advocate's own workspace
+    Given a registered advocate "reader@example.com"
+    When they sign in with the right password
+    Then sign-in succeeds
+    And their own private workspace is named
+  Scenario: A failed sign-in does not reveal whether the account exists
+    Given a registered advocate "reader@example.com"
+    When someone signs in as "reader@example.com" with a wrong password
+    And someone signs in as "nobody@example.com" with any password
+    Then both are refused with exactly the same message
+</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
+          <t>Page/script contract: card content, link order and row, no text below (tests/test_the_page_and_the_script_agree.py, with a planted-failure control). Served sign-in: right password, wrong password, unknown and unreadable account (tests/test_public_email_registration.py). Screenshot of the card. Given/When/Then: tests/features/arrive/F-A-01.feature (run 15 Sep 2026: every scenario passed).</t>
+        </is>
+      </c>
+      <c r="K3" s="4" t="inlineStr">
+        <is>
           <t>Offline test</t>
         </is>
       </c>
-      <c r="K3" s="4" t="inlineStr">
+      <c r="L3" s="4" t="inlineStr">
         <is>
           <t>Contract and its control pass; the four refusals are identical.</t>
         </is>
       </c>
-      <c r="L3" s="4" t="inlineStr">
+      <c r="M3" s="4" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="M3" s="4" t="inlineStr">
+      <c r="N3" s="4" t="inlineStr">
         <is>
           <t>Built</t>
         </is>
       </c>
-      <c r="N3" s="4" t="inlineStr">
-        <is>
-          <t>Pass — offline run 15 Sep 2026 on branch codex/arrive-sign-in: test_the_page_and_the_script_agree.py, test_public_email_registration.py. Full build gate: not yet run.</t>
-        </is>
-      </c>
       <c r="O3" s="4" t="inlineStr">
+        <is>
+          <t>Passed 4 of 4 when the product owner ran them on 15 Sep 2026. The sign-in and register cards changed afterwards (F-A-09 privacy notice, F-A-10 show password, F-A-13 layout), so that run no longer covers them. Not re-run.</t>
+        </is>
+      </c>
+      <c r="P3" s="4" t="inlineStr">
         <is>
           <t>Browser journey (a real browser driving the served page) not run: needs your approval.</t>
         </is>
@@ -801,35 +859,64 @@
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
-          <t>Contract: exactly three inputs, rules present, no other text, passwords cleared before the request. Served: new account, duplicate, mismatch, weak password, oversized input, foreign origin, admission limits (tests/test_public_email_registration.py).</t>
+          <t xml:space="preserve">  Scenario: The register card shows the registration details and the privacy notice
+    Given the sign-in page
+    Then the register card has exactly an email field, a password field, a retype-password field and two privacy boxes
+    And the register card has a Register button and a Back to sign in link
+    And the register card states the password rules
+    And the register card carries no logo and no other text than the privacy notice and its boxes
+  Scenario: Email and password create an account without an invitation
+    When a visitor registers "new@example.com" with a valid password typed twice
+    Then the account is created
+    And the response carries no recovery code or any other secret
+    And they can sign in with that email and password
+  Scenario: Mismatched passwords create nothing
+    When a visitor registers "typo@example.com" with two different passwords
+    Then registration is refused with "do not match"
+    And no account exists for "typo@example.com"
+  Scenario: A password that breaks the rules creates nothing
+    When a visitor registers "weak@example.com" with the password "weak"
+    Then registration is refused naming the password rule
+    And no account exists for "weak@example.com"
+  Scenario: Registering an email twice never replaces the first password
+    Given a registered advocate "reader@example.com"
+    When a visitor registers "READER@example.com" again with a different password
+    Then registration is refused without saying the account exists
+    And the original password still signs in
+</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
         <is>
+          <t>Contract: exactly three inputs, rules present, no other text, passwords cleared before the request. Served: new account, duplicate, mismatch, weak password, oversized input, foreign origin, admission limits (tests/test_public_email_registration.py). Given/When/Then: tests/features/arrive/F-A-02.feature (run 15 Sep 2026: every scenario passed).</t>
+        </is>
+      </c>
+      <c r="K4" s="4" t="inlineStr">
+        <is>
           <t>Offline test</t>
         </is>
       </c>
-      <c r="K4" s="4" t="inlineStr">
+      <c r="L4" s="4" t="inlineStr">
         <is>
           <t>Every registration test and planted-failure control passes.</t>
         </is>
       </c>
-      <c r="L4" s="4" t="inlineStr">
+      <c r="M4" s="4" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="M4" s="4" t="inlineStr">
+      <c r="N4" s="4" t="inlineStr">
         <is>
           <t>Built</t>
         </is>
       </c>
-      <c r="N4" s="4" t="inlineStr">
-        <is>
-          <t>Pass — offline run 15 Sep 2026 on branch codex/arrive-sign-in: test_public_email_registration.py, test_the_page_and_the_script_agree.py. Full build gate: not yet run.</t>
-        </is>
-      </c>
       <c r="O4" s="4" t="inlineStr">
+        <is>
+          <t>Passed 5 of 5 when the product owner ran them on 15 Sep 2026. The sign-in and register cards changed afterwards (F-A-09 privacy notice, F-A-10 show password, F-A-13 layout), so that run no longer covers them. Not re-run.</t>
+        </is>
+      </c>
+      <c r="P4" s="4" t="inlineStr">
         <is>
           <t>Browser journey (a real browser driving the served page) not run: needs your approval.</t>
         </is>
@@ -874,37 +961,73 @@
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
-          <t>tests/test_password_reset_by_email.py: one answer for known, unknown and no-email accounts; single use; expiry; superseded link; passwords checked first; sessions ended; no secret in the clear on disk; configured public URL wins over the Host header; limits per address and per source; two workers cannot both spend one link; sealed outbox. tests/test_the_sign_in_surface_keeps_no_secrets.py: the link's token leaves the address bar and the page.</t>
+          <t xml:space="preserve">  Scenario: The same answer whether or not the account exists
+    Given a registered advocate "reader@example.com"
+    When someone asks for a reset link for "reader@example.com"
+    And someone asks for a reset link for "nobody@example.com"
+    Then both get exactly the same answer
+    And a reset email is queued only for the registered account
+  Scenario: The link sets a new password once and signs out every device
+    Given a registered advocate "reader@example.com" signed in on two devices
+    And a reset link was sent to "reader@example.com"
+    When the link is used to set a new valid password
+    Then the password is changed and both earlier sessions are signed out
+    And the old password no longer signs in
+    And the new password signs in
+    And using the same link again changes nothing
+  Scenario: An expired link changes nothing
+    Given a registered advocate "reader@example.com"
+    And a reset link was sent to "reader@example.com"
+    When the link is used 31 minutes later
+    Then it is refused as not valid or expired
+    And the original password still signs in
+  Scenario: Mismatched new passwords do not use up the link
+    Given a registered advocate "reader@example.com"
+    And a reset link was sent to "reader@example.com"
+    When the link is used with two different new passwords
+    Then it is refused with "do not match"
+    And the link still works afterwards
+  Scenario: The link and the new password are never stored readable
+    Given a registered advocate "reader@example.com"
+    And a reset link was sent to "reader@example.com"
+    When the link is used to set a new valid password
+    Then neither the link nor the new password appears readable in any stored file
+</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
         <is>
+          <t>tests/test_password_reset_by_email.py: one answer for known, unknown and no-email accounts; single use; expiry; superseded link; passwords checked first; sessions ended; no secret in the clear on disk; configured public URL wins over the Host header; limits per address and per source; two workers cannot both spend one link; sealed outbox. tests/test_the_sign_in_surface_keeps_no_secrets.py: the link's token leaves the address bar and the page. Given/When/Then: tests/features/arrive/F-A-03.feature (run 15 Sep 2026: every scenario passed).</t>
+        </is>
+      </c>
+      <c r="K5" s="4" t="inlineStr">
+        <is>
           <t>Offline test</t>
         </is>
       </c>
-      <c r="K5" s="4" t="inlineStr">
+      <c r="L5" s="4" t="inlineStr">
         <is>
           <t>All pass, each rule with the failure it refuses.</t>
         </is>
       </c>
-      <c r="L5" s="4" t="inlineStr">
+      <c r="M5" s="4" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="M5" s="4" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
       <c r="N5" s="4" t="inlineStr">
         <is>
-          <t>Pass — offline run 15 Sep 2026 on branch codex/arrive-sign-in: test_password_reset_by_email.py, test_the_sign_in_surface_keeps_no_secrets.py. Full build gate: not yet run.</t>
+          <t>Built + eval passing</t>
         </is>
       </c>
       <c r="O5" s="4" t="inlineStr">
         <is>
-          <t>Real email delivery is PENDING — see F-A-06. Until then reset emails go to a sealed local outbox on the server; an operator reads one with backend/operations/outbox.py --email &lt;address&gt;. Browser journey (a real browser driving the served page) not run: needs your approval.</t>
+          <t>PASS — run by the product owner on 15 Sep 2026: tests/features/arrive/F-A-03.feature, 5 of 5 scenarios passed (python -m pytest tests/test_arrive_sign_in_features.py -v: 23 passed in 6.74 s). The other test files named in Eval passed in an earlier offline run on 15 Sep 2026; the full test suite has not been run. Re-run needed: the registration route and the sign-in page changed after this run (F-A-09, F-A-10, F-A-12, F-A-13).</t>
+        </is>
+      </c>
+      <c r="P5" s="4" t="inlineStr">
+        <is>
+          <t>Real email delivery is F-A-06 (agreed, not started). Until then reset emails go to a sealed local outbox; an operator reads one with backend/operations/outbox.py --email &lt;address&gt;. Browser journey (a real browser driving the served page) not run: needs your approval.</t>
         </is>
       </c>
     </row>
@@ -947,35 +1070,51 @@
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
-          <t>Whole-product sweep of served routes, backend code, page and script, with a control that plants each kind of return; legacy-account clean-up test (tests/test_account_access_and_workspace.py).</t>
+          <t xml:space="preserve">  Scenario: Nothing in the product offers, issues or accepts a recovery code
+    When the served routes, the backend code, the page and the script are searched
+    Then no recovery code is found anywhere
+  Scenario: The sign-in page has no recovery-code option
+    Given the sign-in page
+    Then there is no "Use a recovery code" link and no recovery-code form
+  Scenario: An older account's recovery-code data is removed at its next sign-in
+    Given an older account that still holds recovery-code data
+    When it signs in with its password
+    Then the recovery-code data is gone from its record
+    And its password is unchanged
+</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
+          <t>Whole-product sweep of served routes, backend code, page and script, with a control that plants each kind of return; legacy-account clean-up test (tests/test_account_access_and_workspace.py). Given/When/Then: tests/features/arrive/F-A-04.feature (run 15 Sep 2026: every scenario passed).</t>
+        </is>
+      </c>
+      <c r="K6" s="4" t="inlineStr">
+        <is>
           <t>Offline test</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Sweep finds 0 sites; the control finds every planted one.</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="M6" s="4" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
       <c r="N6" s="4" t="inlineStr">
         <is>
-          <t>Pass — offline run 15 Sep 2026 on branch codex/arrive-sign-in: test_account_access_and_workspace.py. Full build gate: not yet run.</t>
-        </is>
-      </c>
-      <c r="O6" s="4" t="inlineStr"/>
+          <t>Built + eval passing</t>
+        </is>
+      </c>
+      <c r="O6" s="4" t="inlineStr">
+        <is>
+          <t>PASS — run by the product owner on 15 Sep 2026: tests/features/arrive/F-A-04.feature, 3 of 3 scenarios passed (python -m pytest tests/test_arrive_sign_in_features.py -v: 23 passed in 6.74 s). The other test files named in Eval passed in an earlier offline run on 15 Sep 2026; the full test suite has not been run. Re-run needed: the registration route and the sign-in page changed after this run (F-A-09, F-A-10, F-A-12, F-A-13).</t>
+        </is>
+      </c>
+      <c r="P6" s="4" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
@@ -1016,35 +1155,54 @@
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
-          <t>Contract counts logo marks on the sign-in page — exactly one, on the left — with a planted second-logo control (tests/test_the_page_and_the_script_agree.py); screenshot.</t>
+          <t xml:space="preserve">  Scenario: The sign-in page shows the wordmark once, on the left
+    Given the sign-in page
+    Then the logo appears exactly once
+    And it is on the left panel
+  Scenario Outline: No card on the right repeats the logo
+    Given the sign-in page
+    Then the &lt;card&gt; card carries no logo
+    Examples:
+      | card             |
+      | sign-in          |
+      | register         |
+      | forgot-password  |
+      | set-new-password |
+      | result           |
+</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
         <is>
+          <t>Contract counts logo marks on the sign-in page — exactly one, on the left — with a planted second-logo control (tests/test_the_page_and_the_script_agree.py); screenshot. Given/When/Then: tests/features/arrive/F-A-05.feature (run 15 Sep 2026: every scenario passed).</t>
+        </is>
+      </c>
+      <c r="K7" s="4" t="inlineStr">
+        <is>
           <t>Offline test</t>
         </is>
       </c>
-      <c r="K7" s="4" t="inlineStr">
+      <c r="L7" s="4" t="inlineStr">
         <is>
           <t>Exactly one; the control catches a planted second logo.</t>
         </is>
       </c>
-      <c r="L7" s="4" t="inlineStr">
+      <c r="M7" s="4" t="inlineStr">
         <is>
           <t>Pilot</t>
         </is>
       </c>
-      <c r="M7" s="4" t="inlineStr">
-        <is>
-          <t>Built</t>
-        </is>
-      </c>
       <c r="N7" s="4" t="inlineStr">
         <is>
-          <t>Pass — offline run 15 Sep 2026 on branch codex/arrive-sign-in: test_the_page_and_the_script_agree.py. Full build gate: not yet run.</t>
-        </is>
-      </c>
-      <c r="O7" s="4" t="inlineStr"/>
+          <t>Built + eval passing</t>
+        </is>
+      </c>
+      <c r="O7" s="4" t="inlineStr">
+        <is>
+          <t>PASS — run by the product owner on 15 Sep 2026: tests/features/arrive/F-A-05.feature, 6 of 6 scenarios passed (python -m pytest tests/test_arrive_sign_in_features.py -v: 23 passed in 6.74 s). The other test files named in Eval passed in an earlier offline run on 15 Sep 2026; the full test suite has not been run. Re-run needed: the registration route and the sign-in page changed after this run (F-A-09, F-A-10, F-A-12, F-A-13).</t>
+        </is>
+      </c>
+      <c r="P7" s="4" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="4" t="inlineStr">
@@ -1055,7 +1213,7 @@
       <c r="B8" s="4" t="n"/>
       <c r="C8" s="4" t="inlineStr">
         <is>
-          <t>Send the email to the registered email. Record this and keep it as pending; we will pick it up in future.</t>
+          <t>Send the email to the registered email. Record this and keep it as pending; we will pick it up in future. Update, 15 September 2026: send either a link or a code to the registered email; it is in the plan and we will implement it. Follow-up 3, 15 September 2026: use haaruln@gmail.com to send mails through Gmail.</t>
         </is>
       </c>
       <c r="D8" s="4" t="inlineStr">
@@ -1083,255 +1241,1289 @@
           <t>Send the email through an unapproved provider; send it to any address other than the one registered; build the link from the request's Host header; tell the person asking whether the account exists.</t>
         </is>
       </c>
-      <c r="I8" s="4" t="inlineStr">
-        <is>
-          <t>To be written when picked up: delivery to a test mailbox through the approved provider, a refused unapproved provider, and the configured public link.</t>
-        </is>
-      </c>
+      <c r="I8" s="4" t="n"/>
       <c r="J8" s="4" t="inlineStr">
         <is>
+          <t>To be written once the decisions are made: delivery to a test mailbox through the approved provider; an unapproved provider refused; the link opens the configured public address; the person asking learns nothing about whether the account exists.</t>
+        </is>
+      </c>
+      <c r="K8" s="4" t="inlineStr">
+        <is>
           <t>Offline test</t>
         </is>
       </c>
-      <c r="K8" s="4" t="inlineStr">
+      <c r="L8" s="4" t="inlineStr">
         <is>
           <t>To be set when picked up.</t>
         </is>
       </c>
-      <c r="L8" s="4" t="inlineStr">
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P8" s="4" t="inlineStr">
+        <is>
+          <t>DECIDED: send from haaruln@gmail.com through Gmail. NOT STARTED. Before building: (1) the product owner creates a Gmail App Password (Google Account &gt; Security &gt; 2-Step Verification &gt; App passwords) and puts it in .env themselves — it is never pasted into a chat; (2) Gmail is Google, a processor outside India: it must be approved in docs/blueprint/processors.yaml and the egress policy, which today admits only local processors; (3) a personal Gmail sends about 500 messages a day and its mail can land in spam — a Nyaymalaw-domain sender is the production answer; (4) NM_PUBLIC_URL for the links. Until built, reset emails go to the sealed local outbox.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B9" s="4" t="n"/>
+      <c r="C9" s="4" t="inlineStr">
+        <is>
+          <t>Once the email link or code is done, anyone can register with someone else's email — this will be gone. Follow-up 3, 15 September 2026: yes — the email must be confirmed before the account works.</t>
+        </is>
+      </c>
+      <c r="D9" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E9" s="4" t="inlineStr">
+        <is>
+          <t>F-A-07</t>
+        </is>
+      </c>
+      <c r="F9" s="4" t="inlineStr">
+        <is>
+          <t>Confirm the email address before the account can be used</t>
+        </is>
+      </c>
+      <c r="G9" s="4" t="inlineStr">
+        <is>
+          <t>After registering, the advocate gets a message at that address and confirms it (proposed: a 6-digit code, because many register on a phone and read email on a desktop). Until confirmed the account cannot sign in; the page says what to do and offers to resend.</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="inlineStr">
+        <is>
+          <t>Let an unconfirmed account sign in or hold matter material; let someone who does not control an address keep it registered; say whether an address is already registered.</t>
+        </is>
+      </c>
+      <c r="I9" s="4" t="n"/>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>Draft: sign-in before confirming is refused with instructions; wrong, expired and reused codes are refused; an unconfirmed registration by someone else does not block the real owner.</t>
+        </is>
+      </c>
+      <c r="K9" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>To be set when the row is finalized.</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P9" s="4" t="inlineStr">
+        <is>
+          <t>DECIDED: yes. Depends on F-A-06 (mail delivery). Proposed, not yet confirmed: a 6-digit code rather than a link, because many advocates register on a phone and read email on a desktop; and how long an unconfirmed registration holds the address before it is released.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="n"/>
+      <c r="C10" s="4" t="inlineStr">
+        <is>
+          <t>For register and login we will only use email. Once a person is logged in, we will create a profile page inside the application where we capture details like advocate ID, mobile number and so on. Follow-up 3, 15 September 2026: let both work.</t>
+        </is>
+      </c>
+      <c r="D10" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E10" s="4" t="inlineStr">
+        <is>
+          <t>F-A-08</t>
+        </is>
+      </c>
+      <c r="F10" s="4" t="inlineStr">
+        <is>
+          <t>Sign in with an email address or an existing advocate ID; register with email only</t>
+        </is>
+      </c>
+      <c r="G10" s="4" t="inlineStr">
+        <is>
+          <t>The sign-in field accepts an email address, or an advocate ID for an account that already has one (for example one an operator enrolled). Registration accepts an email address only. Advocate ID and other professional details are captured later on the profile page (F-A-16).</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="inlineStr">
+        <is>
+          <t>Create a new account named by anything other than an email address; tell the person which of the two, name or password, was wrong.</t>
+        </is>
+      </c>
+      <c r="I10" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The sign-in field takes an email address or an advocate ID
+    Given the sign-in page
+    Then the sign-in field is labelled "Email or advocate ID" and does not insist on an email address
+  Scenario: An account that has an advocate ID signs in with it
+    Given an existing account with the advocate ID "adv_legacy"
+    When they sign in with that advocate ID and the right password
+    Then sign-in succeeds
+  Scenario: Registration takes only an email address
+    When a visitor tries to register with "adv_newcomer" instead of an email address
+    Then registration is refused asking for an email address
+    And no account exists for "adv_newcomer"
+</t>
+        </is>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-08.feature (3 scenarios).</t>
+        </is>
+      </c>
+      <c r="K10" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass.</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead).</t>
+        </is>
+      </c>
+      <c r="P10" s="4" t="inlineStr">
+        <is>
+          <t>The product already behaved this way; the sign-in field keeps the label "Email or advocate ID".</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B11" s="4" t="n"/>
+      <c r="C11" s="4" t="inlineStr">
+        <is>
+          <t>Privacy notice and consent at registration — we should absolutely do that. Based on your understanding of India's data protection laws and legal things, prepare a note. Follow-up 3, 15 September 2026: privacy contact haaruln@gmail.com; Nyaymalaw signs the contract through Rahul Lambade, Founder &amp; CEO.</t>
+        </is>
+      </c>
+      <c r="D11" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E11" s="4" t="inlineStr">
+        <is>
+          <t>F-A-09</t>
+        </is>
+      </c>
+      <c r="F11" s="4" t="inlineStr">
+        <is>
+          <t>Privacy notice and consent at registration</t>
+        </is>
+      </c>
+      <c r="G11" s="4" t="inlineStr">
+        <is>
+          <t>The register card shows the notice itself: each detail kept and what it is for (email address, password, sign-ins); how to withdraw consent; how to see, correct or erase the details or raise a grievance, by writing to haaruln@gmail.com; how to complain to the Data Protection Board of India; and that Nyaymalaw is responsible, through Rahul Lambade, Founder &amp; CEO. Two unticked boxes follow: consent, and 18 or older. Register stays unavailable until both are ticked. The consent is recorded with the account: the notice version shown, the time, and the 18-or-older confirmation.</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="inlineStr">
+        <is>
+          <t>Pre-tick a box; put the notice only behind a link; create an account without a recorded consent; use account details for anything the notice does not name.</t>
+        </is>
+      </c>
+      <c r="I11" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The register card shows the privacy notice itself, not a link to it
+    Given the sign-in page
+    Then the register card's notice names each detail kept and what it is for
+    And the notice says how to withdraw consent, how to see, correct or erase the details, and how to complain to the Data Protection Board of India
+    And the notice names Nyaymalaw, through Rahul Lambade, Founder &amp; CEO, and the contact haaruln@gmail.com
+    And the consent box and the 18-or-older box start unticked
+  Scenario: Register waits for both boxes and sends them with the notice version
+    Given the sign-in page
+    Then the Register button stays unavailable until both boxes are ticked
+    And the registration sends both boxes and the notice version the page shows
+    And the notice version on the page is the one the server records
+  Scenario Outline: A registration without full consent creates nothing
+    When a visitor registers "&lt;email&gt;" &lt;gap&gt;
+    Then registration is refused and nothing was saved
+    And no account exists for "&lt;email&gt;"
+    Examples:
+      | email                 | gap                                        |
+      | noconsent@example.com | without agreeing to the privacy notice     |
+      | minor@example.com     | without confirming they are 18 or older    |
+      | stale@example.com     | agreeing to an older version of the notice |
+      | absent@example.com    | sending no consent at all                  |
+  Scenario: The consent is recorded with the account
+    When a visitor registers "consent@example.com" with a valid password typed twice
+    Then the account record holds the notice version, the time of consent and the 18-or-older confirmation
+</t>
+        </is>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-09.feature (4 scenarios, one of them run for 4 ways of sending incomplete consent). Counsel reviews the wording.</t>
+        </is>
+      </c>
+      <c r="K11" s="4" t="inlineStr">
+        <is>
+          <t>Human expert</t>
+        </is>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; counsel confirms the notice.</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). Counsel review not started.</t>
+        </is>
+      </c>
+      <c r="P11" s="4" t="inlineStr">
+        <is>
+          <t>Note for counsel: https://claude.ai/artifact/45EEj9RTM28C1aoziVx8tL. Open: (1) accounts made without the register card — operator enrolment (backend/operations/enrol.py) and invitations — carry no consent; proposal: ask for consent at their next sign-in; (2) a personal Gmail as the privacy and grievance contact — proposal: a role address on a Nyaymalaw domain later; (3) counsel's answers to the six questions in the note. Changing the notice's words needs a new PRIVACY_NOTICE_VERSION (backend/nm/domain/advocate.py) and the same value on the card. Core duties apply from 14 May 2027.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B12" s="4" t="n"/>
+      <c r="C12" s="4" t="inlineStr">
+        <is>
+          <t>Show password button in the sign-in card — absolutely we should add this.</t>
+        </is>
+      </c>
+      <c r="D12" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E12" s="4" t="inlineStr">
+        <is>
+          <t>F-A-10</t>
+        </is>
+      </c>
+      <c r="F12" s="4" t="inlineStr">
+        <is>
+          <t>Show or hide the password on the sign-in card</t>
+        </is>
+      </c>
+      <c r="G12" s="4" t="inlineStr">
+        <is>
+          <t>An eye button beside the sign-in password shows and hides what was typed, the same as on Register and Set a new password.</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="inlineStr">
+        <is>
+          <t>Send the form when pressed; leave the password on the card, shown or hidden, after signing in, a refused sign-in, or leaving the card.</t>
+        </is>
+      </c>
+      <c r="I12" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The sign-in card has a show-password button that never sends the form
+    Given the sign-in page
+    Then the sign-in password field has an eye button beside it, labelled "Show password"
+    And every eye button on the page is a plain button that cannot send its form
+  Scenario: The password is put away whenever it could be left showing
+    Given the page script
+    Then a sign-in that succeeds and one that is refused both clear and mask the password
+    And leaving the sign-in card clears and masks the password
+    And every card puts its passwords away the same way
+</t>
+        </is>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-10.feature (2 scenarios).</t>
+        </is>
+      </c>
+      <c r="K12" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass.</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead).</t>
+        </is>
+      </c>
+      <c r="P12" s="4" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B13" s="4" t="n"/>
+      <c r="C13" s="4" t="inlineStr">
+        <is>
+          <t>Two-step sign-in — park this for now; we will come back to it later.</t>
+        </is>
+      </c>
+      <c r="D13" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E13" s="4" t="inlineStr">
+        <is>
+          <t>F-A-11</t>
+        </is>
+      </c>
+      <c r="F13" s="4" t="inlineStr">
+        <is>
+          <t>Two-step sign-in</t>
+        </is>
+      </c>
+      <c r="G13" s="4" t="inlineStr">
+        <is>
+          <t>To be described when picked up (for example a code from an authenticator app after the password).</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="inlineStr">
+        <is>
+          <t>To be described when picked up.</t>
+        </is>
+      </c>
+      <c r="I13" s="4" t="n"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>To be written when picked up.</t>
+        </is>
+      </c>
+      <c r="K13" s="4" t="inlineStr"/>
+      <c r="L13" s="4" t="inlineStr"/>
+      <c r="M13" s="4" t="inlineStr">
         <is>
           <t>Later</t>
         </is>
       </c>
-      <c r="M8" s="4" t="inlineStr">
+      <c r="N13" s="4" t="inlineStr">
         <is>
           <t>Not started</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
+      <c r="O13" s="4" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>PENDING — product owner, 15 September 2026: to be picked up in future. Needs a mail provider chosen and approved, and NM_PUBLIC_URL set. Until then F-A-03 writes reset emails to the sealed local outbox.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
+      <c r="P13" s="4" t="inlineStr">
+        <is>
+          <t>PARKED by the product owner, 15 September 2026. The control plane already lists it as a production release requirement (BK-42), so it must return before a production release.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B14" s="4" t="n"/>
+      <c r="C14" s="4" t="inlineStr">
+        <is>
+          <t>Session length — make it just three hours. After three hours, the advocate should log in again. Follow-up 3, 15 September 2026: make it 30 min of inactivity, meaning there is no activity — no typing, moving cursor, opening some tabs — none of that; the app/website window was not touched at all for 30 mins — then sign out. When there is activity, the clock lapses and resets at the beginning of the next inactivity. Decision, 15 September 2026: keep the 12 hour limit.</t>
+        </is>
+      </c>
+      <c r="D14" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E14" s="4" t="inlineStr">
+        <is>
+          <t>F-A-12</t>
+        </is>
+      </c>
+      <c r="F14" s="4" t="inlineStr">
+        <is>
+          <t>Sign out after 30 minutes without activity</t>
+        </is>
+      </c>
+      <c r="G14" s="4" t="inlineStr">
+        <is>
+          <t>Typing, moving the pointer, touching, scrolling and coming back to the tab all count as activity, in any open tab, and any activity starts the 30 minutes again. Two minutes before, a warning says when the sign-out will happen. After 30 untouched minutes the page signs out, ends the session on the server, and keeps anything typed but not sent, putting it back after signing in again. The server keeps the same 30-minute clock, so a session on a closed laptop stops working on its own. However active, a session still ends 12 hours after signing in.</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="inlineStr">
+        <is>
+          <t>Keep a session usable after 30 minutes with no activity; let activity after the 30 minutes start them again (opening a laptop hours later signs out); count a refused request as activity; lose an unsent brief when the session ends; show matter content once the session has ended.</t>
+        </is>
+      </c>
+      <c r="I14" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: A session left untouched for 30 minutes stops working
+    Given an advocate who is signed in
+    When nothing uses the session for 30 minutes
+    Then the session is refused
+  Scenario: Using the app starts the 30 minutes again
+    Given an advocate who is signed in
+    When they use the app every 29 minutes for two hours
+    Then the session still works
+  Scenario: However busy, a session ends 12 hours after signing in
+    Given an advocate who is signed in
+    When they use the app every 29 minutes until 12 hours after signing in
+    Then the session is refused
+  Scenario: The page signs out after 30 untouched minutes and keeps the draft
+    Given the page script
+    Then typing, pointing, touching, scrolling and coming back to the tab all count as activity
+    And the 30 minutes come from the server and are not written in the page
+    And activity in one open tab counts for every open tab
+    And a warning appears 2 minutes before the sign-out
+    And activity after the 30 minutes signs out instead of starting them again
+    And the idle sign-out keeps the unsent draft and ends the session on the server
+</t>
+        </is>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-12.feature (4 scenarios) and tests/test_authentication.py (idle limit, activity starting it again, a refused presentation, no revival of an ended session).</t>
+        </is>
+      </c>
+      <c r="K14" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios and tests pass.</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead).</t>
+        </is>
+      </c>
+      <c r="P14" s="4" t="inlineStr">
+        <is>
+          <t>DECIDED 15 September 2026: the 12-hour limit is kept alongside the 30 minutes. Watching the warning and the sign-out in a real browser needs your go-ahead. Four existing tests that move the clock two hours now sign in again afterwards.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B15" s="4" t="n"/>
+      <c r="C15" s="4" t="inlineStr">
+        <is>
+          <t>Advocates will sign in from desktop, phones as well as tablets, so we should be prepared for all three views. Follow-up 3, 15 September 2026: widths — ok.</t>
+        </is>
+      </c>
+      <c r="D15" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E15" s="4" t="inlineStr">
+        <is>
+          <t>F-A-13</t>
+        </is>
+      </c>
+      <c r="F15" s="4" t="inlineStr">
+        <is>
+          <t>The sign-in page works on desktop, tablet and phone</t>
+        </is>
+      </c>
+      <c r="G15" s="4" t="inlineStr">
+        <is>
+          <t>Phone (about 360–430 px) and portrait tablet (up to 820 px): one column, the logo above the card, the left panel's story text set aside. Landscape tablet (821–1024 px): two columns, the left panel and the gap narrowed. Desktop (1280 px and wider) as today. Every card is fully usable without scrolling sideways, and a card taller than the screen scrolls to its top.</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="inlineStr">
+        <is>
+          <t>Push the sign-in card below a screen-filling panel on a phone; clip or overlap text; need sideways scrolling.</t>
+        </is>
+      </c>
+      <c r="I15" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: On a phone or portrait tablet the logo sits above the card
+    Given the sign-in page
+    And the page stylesheet
+    Then at 820 px wide or narrower the sign-in page is one column
+    And the left panel keeps only its logo and the logo is not hidden
+    And the logo appears exactly once
+  Scenario: On a landscape tablet the two columns narrow before the card does
+    Given the page stylesheet
+    Then between 821 and 1024 px wide the left panel and the gap beside it are narrower
+  Scenario: A card taller than the screen can be scrolled to its top
+    Given the page stylesheet
+    Then the sign-in page centres its cards with auto margins, not by aligning to the middle of a scrolling area
+  Scenario: No card needs sideways scrolling on a 360 px phone
+    Given the page stylesheet
+    Then the cards are at most 420 px wide and shrink with the screen
+</t>
+        </is>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-13.feature (4 scenarios, read from the stylesheet). Still to do: a real browser opens each card at 390, 768, 1024 and 1280 px and saves a screenshot of each.</t>
+        </is>
+      </c>
+      <c r="K15" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; the screenshots show nothing clipped, overlapping or scrolling sideways.</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). Browser screenshots need your go-ahead.</t>
+        </is>
+      </c>
+      <c r="P15" s="4" t="inlineStr">
+        <is>
+          <t>The top ribbon and home page (F-A-17, F-A-18) need the same three widths.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B16" s="4" t="n"/>
+      <c r="C16" s="4" t="inlineStr">
+        <is>
+          <t>Add all the above features to the implementation plan under the Arrive phase (proposed in the privacy note).</t>
+        </is>
+      </c>
+      <c r="D16" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E16" s="4" t="inlineStr">
+        <is>
+          <t>F-A-14</t>
+        </is>
+      </c>
+      <c r="F16" s="4" t="inlineStr">
+        <is>
+          <t>Withdraw consent and delete the account</t>
+        </is>
+      </c>
+      <c r="G16" s="4" t="inlineStr">
+        <is>
+          <t>From the profile page an advocate withdraws consent and deletes the account in no more steps than registering took; every session ends and processors are told to stop.</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="inlineStr">
+        <is>
+          <t>Make deleting harder than registering; keep processing account data after withdrawal except where the law requires it.</t>
+        </is>
+      </c>
+      <c r="I16" s="4" t="n"/>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>Draft: after deletion, sign-in is refused, sessions are ended and account data is erased or scheduled for erasure under the agreed retention period.</t>
+        </is>
+      </c>
+      <c r="K16" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>To be set when the row is finalized.</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P16" s="4" t="inlineStr">
+        <is>
+          <t>Depends on the profile page (F-A-16) and counsel's retention answer.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B17" s="4" t="n"/>
+      <c r="C17" s="4" t="inlineStr">
+        <is>
+          <t>Add all the above features to the implementation plan under the Arrive phase (proposed in the privacy note).</t>
+        </is>
+      </c>
+      <c r="D17" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E17" s="4" t="inlineStr">
+        <is>
+          <t>F-A-15</t>
+        </is>
+      </c>
+      <c r="F17" s="4" t="inlineStr">
+        <is>
+          <t>See, correct or erase my details, and raise a grievance</t>
+        </is>
+      </c>
+      <c r="G17" s="4" t="inlineStr">
+        <is>
+          <t>From the profile page an advocate sees the account details held, corrects them, asks for erasure, and raises a grievance to a named contact, tracked to a response within 90 days.</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="inlineStr">
+        <is>
+          <t>Leave a request without an owner or a due date; show one advocate's details to another.</t>
+        </is>
+      </c>
+      <c r="I17" s="4" t="n"/>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>Draft: each request type is recorded with an owner and due date; access is own-account only.</t>
+        </is>
+      </c>
+      <c r="K17" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>To be set when the row is finalized.</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P17" s="4" t="inlineStr">
+        <is>
+          <t>Depends on the profile page (F-A-16) and a named grievance contact.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="n"/>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>Once a person is logged in, we will create a profile page inside the application where we will capture some of the details like advocate ID, mobile number and so on. Keep this in the back of your mind; we will build it in the profile page.</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>F-A-16</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>Profile page</t>
+        </is>
+      </c>
+      <c r="G18" s="4" t="inlineStr">
+        <is>
+          <t>To be described by the product owner: advocate enrolment number, mobile number and other details, kept inside the application after sign-in.</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="inlineStr">
+        <is>
+          <t>To be described.</t>
+        </is>
+      </c>
+      <c r="I18" s="4" t="n"/>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>To be written when described.</t>
+        </is>
+      </c>
+      <c r="K18" s="4" t="inlineStr"/>
+      <c r="L18" s="4" t="inlineStr"/>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Later</t>
+        </is>
+      </c>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>Not started</t>
+        </is>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="P18" s="4" t="inlineStr">
+        <is>
+          <t>To be described in a later stage. F-A-14 and F-A-15 live on this page.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B19" s="4" t="n"/>
+      <c r="C19" s="4" t="inlineStr">
+        <is>
+          <t>For all the pages across Nyaymalaw, this ribbon should be constant and frozen across all the pages: the NM logo, then Nyaymalaw; below that the tabs Home, My work, Legal library (replace Research) and Preparation — only these four. On the right, aligned to Nyaymalaw in the first row the way it is today: the user name (Lambade Rahul), Active workspace — Lambade Rahul's private workspace — and after the name a person's icon with an arrow button that opens a pop-up or small drop-down showing Profile, with all the profile details, and Sign out. Decision, 15 September 2026: go with your ribbon proposals.</t>
+        </is>
+      </c>
+      <c r="D19" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E19" s="4" t="inlineStr">
+        <is>
+          <t>F-A-17</t>
+        </is>
+      </c>
+      <c r="F19" s="4" t="inlineStr">
+        <is>
+          <t>The top ribbon, the same on every page</t>
+        </is>
+      </c>
+      <c r="G19" s="4" t="inlineStr">
+        <is>
+          <t>Stays at the top of every page after sign-in; no page is shown without it. Row 1: the NM logo and Nyaymalaw on the left; on the right the advocate's name (or email while the account has no name), Active workspace with its name, and a person icon with an arrow. The person menu shows the profile details held — name, email, active workspace, enrolment and practice, professional approval — with Signed-in devices and Sign out; it closes on Escape, on a click elsewhere and when the session ends. Row 2: four tabs — Home, My work, Legal library (was Research), Preparation. Case file and History are offered inside My work while a matter is open, and open on that matter. The library availability line is on the Legal library page. On a phone, row 1 shows the logo and the person icon (name and workspace are in the menu), the tabs stay on one row that scrolls sideways, and the Matters button is inside My work.</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="inlineStr">
+        <is>
+          <t>Differ or disappear from one page to another; show another advocate's name or workspace; look signed out when the server has not ended the session.</t>
+        </is>
+      </c>
+      <c r="I19" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The ribbon's first row carries the logo, the advocate and the workspace
+    Given the page
+    Then the ribbon's first row has the NM logo and Nyaymalaw on the left
+    And on its right the advocate's name, the active workspace and a person menu button, in that order
+  Scenario: The ribbon has exactly four tabs
+    Given the page
+    Then the ribbon's tabs are exactly Home, My work, Legal library and Preparation
+  Scenario: The ribbon stays at the top of every page
+    Given the page
+    And the page script
+    And the page stylesheet
+    Then the ribbon is outside every page, and every page scrolls inside itself below it
+    And moving between pages never hides the ribbon; only the sign-in gate does
+  Scenario: The person menu holds the profile, signed-in devices and sign out
+    Given the page
+    And the page script
+    Then the person menu shows the name, email, active workspace, enrolment and practice, and professional approval
+    And the person menu has Signed-in devices and Sign out
+    And the menu opens from its button and closes on Escape, on a click elsewhere, and when the session ends
+  Scenario: Case file and History open from inside My work for the matter that is open
+    Given the page
+    And the page script
+    Then Case file and History are not tabs
+    And My work offers Case file and History only while a matter is open
+    And they open on that matter, with My work still the marked tab
+  Scenario: The Legal library page says whether the library can be read
+    Given the page
+    Then the library availability line is on the Legal library page and not in the ribbon
+  Scenario: On a phone the ribbon keeps the logo and the person menu
+    Given the page
+    And the page stylesheet
+    Then at 820 px wide or narrower the name and workspace move into the person menu
+    And the tabs stay on one row that scrolls inside the ribbon
+    And the Matters button is inside My work
+  Scenario: The ribbon shows only the signed-in account
+    Given the page script
+    Then the name shown is the account's own name, or its email when it has none
+    And ending the session clears the name, the workspace and every profile detail
+</t>
+        </is>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-17.feature (8 scenarios, read from the page, script and stylesheet).</t>
+        </is>
+      </c>
+      <c r="K19" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; the browser journeys pass at 390, 768 and 1280 px.</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). The browser journeys were updated to the new ribbon and to landing on Home (tests/test_the_journey_login_to_logout.py and the journeys that use it) and have not been run.</t>
+        </is>
+      </c>
+      <c r="P19" s="4" t="inlineStr">
+        <is>
+          <t>Profile details beyond those already held (advocate ID, mobile number) come with the profile page, F-A-16, which is parked. Signing out stays the confirmed-or-says-so sign-out it was (BK-40).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="4" t="inlineStr">
+        <is>
+          <t>A. Arrive</t>
+        </is>
+      </c>
+      <c r="B20" s="4" t="n"/>
+      <c r="C20" s="4" t="inlineStr">
+        <is>
+          <t>The home page should be very clean. It should have just one to two lines of introduction — what NM is — and below that a button to start a matter. Do this for now. Decision, 15 September 2026: go with your proposals.</t>
+        </is>
+      </c>
+      <c r="D20" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E20" s="4" t="inlineStr">
+        <is>
+          <t>F-A-18</t>
+        </is>
+      </c>
+      <c r="F20" s="4" t="inlineStr">
+        <is>
+          <t>A clean home page with a short introduction and Start a matter</t>
+        </is>
+      </c>
+      <c r="G20" s="4" t="inlineStr">
+        <is>
+          <t>Two lines: "Nyaymalaw is a legal research and matter workspace for advocates practising Telangana and Union of India law." and "Every answer shows the Act, section or judgment it rests on." Below them one button, Start a matter, which opens a new matter in My work. A sign-in lands on Home, except after a session that ended part-way through a brief, which goes straight back to that brief in My work.</t>
+        </is>
+      </c>
+      <c r="H20" s="4" t="inlineStr">
+        <is>
+          <t>Carry anything else; claim coverage beyond what is held (Telangana and Union of India law).</t>
+        </is>
+      </c>
+      <c r="I20" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The home page is two lines and one button
+    Given the page
+    Then the home page says "Nyaymalaw is a legal research and matter workspace for advocates practising Telangana and Union of India law."
+    And the home page says "Every answer shows the Act, section or judgment it rests on."
+    And the home page has one button, "Start a matter", and nothing else
+  Scenario: Start a matter opens a new matter in My work
+    Given the page script
+    Then the Start a matter button starts a new matter in My work
+  Scenario: A sign-in lands on Home unless a brief was interrupted
+    Given the page script
+    Then a sign-in shows the Home page
+    And a sign-in after a session ended part-way through a brief goes back to that brief in My work
+</t>
+        </is>
+      </c>
+      <c r="J20" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/arrive/F-A-18.feature (3 scenarios).</t>
+        </is>
+      </c>
+      <c r="K20" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L20" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; the browser journeys pass.</t>
+        </is>
+      </c>
+      <c r="M20" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O20" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). The browser journeys were updated to the new ribbon and to landing on Home (tests/test_the_journey_login_to_logout.py and the journeys that use it) and have not been run.</t>
+        </is>
+      </c>
+      <c r="P20" s="4" t="inlineStr">
+        <is>
+          <t>My work keeps its own welcome (Begin with the instruction) for when no matter is open.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
         <is>
           <t>B. Open a matter</t>
         </is>
       </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="B21" s="3" t="inlineStr">
         <is>
           <t>Route, triage, screen conflict, admit substance.</t>
         </is>
       </c>
-      <c r="C9" s="4" t="n"/>
-      <c r="D9" s="4" t="n"/>
-      <c r="E9" s="4" t="n"/>
-      <c r="F9" s="4" t="n"/>
-      <c r="G9" s="4" t="n"/>
-      <c r="H9" s="4" t="n"/>
-      <c r="I9" s="4" t="n"/>
-      <c r="J9" s="4" t="n"/>
-      <c r="K9" s="4" t="n"/>
-      <c r="L9" s="4" t="n"/>
-      <c r="M9" s="4" t="n"/>
-      <c r="N9" s="4" t="n"/>
-      <c r="O9" s="4" t="n"/>
-    </row>
-    <row r="10">
-      <c r="A10" s="2" t="inlineStr">
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+      <c r="G21" s="4" t="n"/>
+      <c r="H21" s="4" t="n"/>
+      <c r="I21" s="4" t="n"/>
+      <c r="J21" s="4" t="n"/>
+      <c r="K21" s="4" t="n"/>
+      <c r="L21" s="4" t="n"/>
+      <c r="M21" s="4" t="n"/>
+      <c r="N21" s="4" t="n"/>
+      <c r="O21" s="4" t="n"/>
+      <c r="P21" s="4" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
         <is>
           <t>C. Take the brief</t>
         </is>
       </c>
-      <c r="B10" s="3" t="inlineStr">
+      <c r="B22" s="3" t="inlineStr">
         <is>
           <t>Account, objectives, parties, threads, chronology, material, evidence.</t>
         </is>
       </c>
-      <c r="C10" s="4" t="n"/>
-      <c r="D10" s="4" t="n"/>
-      <c r="E10" s="4" t="n"/>
-      <c r="F10" s="4" t="n"/>
-      <c r="G10" s="4" t="n"/>
-      <c r="H10" s="4" t="n"/>
-      <c r="I10" s="4" t="n"/>
-      <c r="J10" s="4" t="n"/>
-      <c r="K10" s="4" t="n"/>
-      <c r="L10" s="4" t="n"/>
-      <c r="M10" s="4" t="n"/>
-      <c r="N10" s="4" t="n"/>
-      <c r="O10" s="4" t="n"/>
-    </row>
-    <row r="11">
-      <c r="A11" s="2" t="inlineStr">
+      <c r="C22" s="4" t="n"/>
+      <c r="D22" s="4" t="n"/>
+      <c r="E22" s="4" t="n"/>
+      <c r="F22" s="4" t="n"/>
+      <c r="G22" s="4" t="n"/>
+      <c r="H22" s="4" t="n"/>
+      <c r="I22" s="4" t="n"/>
+      <c r="J22" s="4" t="n"/>
+      <c r="K22" s="4" t="n"/>
+      <c r="L22" s="4" t="n"/>
+      <c r="M22" s="4" t="n"/>
+      <c r="N22" s="4" t="n"/>
+      <c r="O22" s="4" t="n"/>
+      <c r="P22" s="4" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
         <is>
           <t>D. Work the file</t>
         </is>
       </c>
-      <c r="B11" s="3" t="inlineStr">
+      <c r="B23" s="3" t="inlineStr">
         <is>
           <t>Cause, limitation, forum, jurisdiction, deadlines, research, proof, theory.</t>
         </is>
       </c>
-      <c r="C11" s="4" t="n"/>
-      <c r="D11" s="4" t="n"/>
-      <c r="E11" s="4" t="n"/>
-      <c r="F11" s="4" t="n"/>
-      <c r="G11" s="4" t="n"/>
-      <c r="H11" s="4" t="n"/>
-      <c r="I11" s="4" t="n"/>
-      <c r="J11" s="4" t="n"/>
-      <c r="K11" s="4" t="n"/>
-      <c r="L11" s="4" t="n"/>
-      <c r="M11" s="4" t="n"/>
-      <c r="N11" s="4" t="n"/>
-      <c r="O11" s="4" t="n"/>
-    </row>
-    <row r="12">
-      <c r="A12" s="2" t="inlineStr">
+      <c r="C23" s="4" t="n"/>
+      <c r="D23" s="4" t="n"/>
+      <c r="E23" s="4" t="n"/>
+      <c r="F23" s="4" t="n"/>
+      <c r="G23" s="4" t="n"/>
+      <c r="H23" s="4" t="n"/>
+      <c r="I23" s="4" t="n"/>
+      <c r="J23" s="4" t="n"/>
+      <c r="K23" s="4" t="n"/>
+      <c r="L23" s="4" t="n"/>
+      <c r="M23" s="4" t="n"/>
+      <c r="N23" s="4" t="n"/>
+      <c r="O23" s="4" t="n"/>
+      <c r="P23" s="4" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
         <is>
           <t>E. Advise</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B24" s="3" t="inlineStr">
         <is>
           <t>Scenarios, recommendation, proportionality, decision, disagreement.</t>
         </is>
       </c>
-      <c r="C12" s="4" t="n"/>
-      <c r="D12" s="4" t="n"/>
-      <c r="E12" s="4" t="n"/>
-      <c r="F12" s="4" t="n"/>
-      <c r="G12" s="4" t="n"/>
-      <c r="H12" s="4" t="n"/>
-      <c r="I12" s="4" t="n"/>
-      <c r="J12" s="4" t="n"/>
-      <c r="K12" s="4" t="n"/>
-      <c r="L12" s="4" t="n"/>
-      <c r="M12" s="4" t="n"/>
-      <c r="N12" s="4" t="n"/>
-      <c r="O12" s="4" t="n"/>
-    </row>
-    <row r="13">
-      <c r="A13" s="2" t="inlineStr">
+      <c r="C24" s="4" t="n"/>
+      <c r="D24" s="4" t="n"/>
+      <c r="E24" s="4" t="n"/>
+      <c r="F24" s="4" t="n"/>
+      <c r="G24" s="4" t="n"/>
+      <c r="H24" s="4" t="n"/>
+      <c r="I24" s="4" t="n"/>
+      <c r="J24" s="4" t="n"/>
+      <c r="K24" s="4" t="n"/>
+      <c r="L24" s="4" t="n"/>
+      <c r="M24" s="4" t="n"/>
+      <c r="N24" s="4" t="n"/>
+      <c r="O24" s="4" t="n"/>
+      <c r="P24" s="4" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
         <is>
           <t>F. Act</t>
         </is>
       </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="B25" s="3" t="inlineStr">
         <is>
           <t>Negotiate, brief the drafter, draft, file, witnesses, hearing, court.</t>
         </is>
       </c>
-      <c r="C13" s="4" t="n"/>
-      <c r="D13" s="4" t="n"/>
-      <c r="E13" s="4" t="n"/>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
-      <c r="H13" s="4" t="n"/>
-      <c r="I13" s="4" t="n"/>
-      <c r="J13" s="4" t="n"/>
-      <c r="K13" s="4" t="n"/>
-      <c r="L13" s="4" t="n"/>
-      <c r="M13" s="4" t="n"/>
-      <c r="N13" s="4" t="n"/>
-      <c r="O13" s="4" t="n"/>
-    </row>
-    <row r="14">
-      <c r="A14" s="2" t="inlineStr">
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+      <c r="G25" s="4" t="n"/>
+      <c r="H25" s="4" t="n"/>
+      <c r="I25" s="4" t="n"/>
+      <c r="J25" s="4" t="n"/>
+      <c r="K25" s="4" t="n"/>
+      <c r="L25" s="4" t="n"/>
+      <c r="M25" s="4" t="n"/>
+      <c r="N25" s="4" t="n"/>
+      <c r="O25" s="4" t="n"/>
+      <c r="P25" s="4" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
         <is>
           <t>G. Carry</t>
         </is>
       </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="B26" s="3" t="inlineStr">
         <is>
           <t>Proactive service, conflict watch, handover.</t>
         </is>
       </c>
-      <c r="C14" s="4" t="n"/>
-      <c r="D14" s="4" t="n"/>
-      <c r="E14" s="4" t="n"/>
-      <c r="F14" s="4" t="n"/>
-      <c r="G14" s="4" t="n"/>
-      <c r="H14" s="4" t="n"/>
-      <c r="I14" s="4" t="n"/>
-      <c r="J14" s="4" t="n"/>
-      <c r="K14" s="4" t="n"/>
-      <c r="L14" s="4" t="n"/>
-      <c r="M14" s="4" t="n"/>
-      <c r="N14" s="4" t="n"/>
-      <c r="O14" s="4" t="n"/>
-    </row>
-    <row r="15">
-      <c r="A15" s="2" t="inlineStr">
+      <c r="C26" s="4" t="n"/>
+      <c r="D26" s="4" t="n"/>
+      <c r="E26" s="4" t="n"/>
+      <c r="F26" s="4" t="n"/>
+      <c r="G26" s="4" t="n"/>
+      <c r="H26" s="4" t="n"/>
+      <c r="I26" s="4" t="n"/>
+      <c r="J26" s="4" t="n"/>
+      <c r="K26" s="4" t="n"/>
+      <c r="L26" s="4" t="n"/>
+      <c r="M26" s="4" t="n"/>
+      <c r="N26" s="4" t="n"/>
+      <c r="O26" s="4" t="n"/>
+      <c r="P26" s="4" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
         <is>
           <t>H. Close</t>
         </is>
       </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="B27" s="3" t="inlineStr">
         <is>
           <t>Capture events, close and reopen.</t>
         </is>
       </c>
-      <c r="C15" s="4" t="n"/>
-      <c r="D15" s="4" t="n"/>
-      <c r="E15" s="4" t="n"/>
-      <c r="F15" s="4" t="n"/>
-      <c r="G15" s="4" t="n"/>
-      <c r="H15" s="4" t="n"/>
-      <c r="I15" s="4" t="n"/>
-      <c r="J15" s="4" t="n"/>
-      <c r="K15" s="4" t="n"/>
-      <c r="L15" s="4" t="n"/>
-      <c r="M15" s="4" t="n"/>
-      <c r="N15" s="4" t="n"/>
-      <c r="O15" s="4" t="n"/>
-    </row>
-    <row r="16">
-      <c r="A16" s="2" t="inlineStr">
+      <c r="C27" s="4" t="n"/>
+      <c r="D27" s="4" t="n"/>
+      <c r="E27" s="4" t="n"/>
+      <c r="F27" s="4" t="n"/>
+      <c r="G27" s="4" t="n"/>
+      <c r="H27" s="4" t="n"/>
+      <c r="I27" s="4" t="n"/>
+      <c r="J27" s="4" t="n"/>
+      <c r="K27" s="4" t="n"/>
+      <c r="L27" s="4" t="n"/>
+      <c r="M27" s="4" t="n"/>
+      <c r="N27" s="4" t="n"/>
+      <c r="O27" s="4" t="n"/>
+      <c r="P27" s="4" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
         <is>
           <t>I. Leave</t>
         </is>
       </c>
-      <c r="B16" s="3" t="inlineStr">
+      <c r="B28" s="3" t="inlineStr">
         <is>
           <t>End the session and leave nothing behind.</t>
         </is>
       </c>
-      <c r="C16" s="4" t="n"/>
-      <c r="D16" s="4" t="n"/>
-      <c r="E16" s="4" t="n"/>
-      <c r="F16" s="4" t="n"/>
-      <c r="G16" s="4" t="n"/>
-      <c r="H16" s="4" t="n"/>
-      <c r="I16" s="4" t="n"/>
-      <c r="J16" s="4" t="n"/>
-      <c r="K16" s="4" t="n"/>
-      <c r="L16" s="4" t="n"/>
-      <c r="M16" s="4" t="n"/>
-      <c r="N16" s="4" t="n"/>
-      <c r="O16" s="4" t="n"/>
+      <c r="C28" s="4" t="n"/>
+      <c r="D28" s="4" t="n"/>
+      <c r="E28" s="4" t="n"/>
+      <c r="F28" s="4" t="n"/>
+      <c r="G28" s="4" t="n"/>
+      <c r="H28" s="4" t="n"/>
+      <c r="I28" s="4" t="n"/>
+      <c r="J28" s="4" t="n"/>
+      <c r="K28" s="4" t="n"/>
+      <c r="L28" s="4" t="n"/>
+      <c r="M28" s="4" t="n"/>
+      <c r="N28" s="4" t="n"/>
+      <c r="O28" s="4" t="n"/>
+      <c r="P28" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:O16"/>
+  <autoFilter ref="A1:P28"/>
   <dataValidations count="4">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Feature,Phase gate,Whole journey"</formula1>
     </dataValidation>
-    <dataValidation sqref="J2:J500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="K2:K500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Offline test,Corpus,Model-judged,Human expert"</formula1>
     </dataValidation>
-    <dataValidation sqref="L2:L500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Pilot,Production,Later"</formula1>
     </dataValidation>
-    <dataValidation sqref="M2:M500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not started,Built,Built + eval passing"</formula1>
     </dataValidation>
   </dataValidations>

--- a/docs/Nyaymalaw_Implementation_Plan.xlsx
+++ b/docs/Nyaymalaw_Implementation_Plan.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Implementation Plan" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Implementation Plan'!$A$1:$P$28</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Implementation Plan'!$A$1:$P$34</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -556,7 +556,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P28"/>
+  <dimension ref="A1:P35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2126,7 +2126,7 @@
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
-          <t>Stays at the top of every page after sign-in; no page is shown without it. Row 1: the NM logo and Nyaymalaw on the left; on the right the advocate's name (or email while the account has no name), Active workspace with its name, and a person icon with an arrow. The person menu shows the profile details held — name, email, active workspace, enrolment and practice, professional approval — with Signed-in devices and Sign out; it closes on Escape, on a click elsewhere and when the session ends. Row 2: four tabs — Home, My work, Legal library (was Research), Preparation. Case file and History are offered inside My work while a matter is open, and open on that matter. The library availability line is on the Legal library page. On a phone, row 1 shows the logo and the person icon (name and workspace are in the menu), the tabs stay on one row that scrolls sideways, and the Matters button is inside My work.</t>
+          <t>Stays at the top of every page after sign-in; no page is shown without it. Row 1: the NM logo and Nyaymalaw on the left; on the right the advocate's name (or email while the account has no name), Active workspace with its name, and a person icon with an arrow. The person menu shows the profile details held — name, email, active workspace, enrolment and practice, professional approval — with Signed-in devices and Sign out; it closes on Escape, on a click elsewhere and when the session ends. Row 2: four tabs — Home, My work, Legal library (was Research), Preparation. Case file and History are offered inside any open matter, and open on that matter under the tab the matter was reached from. The library availability line is on the Legal library page. On a phone, row 1 shows the logo and the person icon (name and workspace are in the menu), the tabs stay on one row that scrolls sideways, and the Matters button is inside My work.</t>
         </is>
       </c>
       <c r="H19" s="4" t="inlineStr">
@@ -2155,12 +2155,12 @@
     Then the person menu shows the name, email, active workspace, enrolment and practice, and professional approval
     And the person menu has Signed-in devices and Sign out
     And the menu opens from its button and closes on Escape, on a click elsewhere, and when the session ends
-  Scenario: Case file and History open from inside My work for the matter that is open
+  Scenario: Case file and History open from inside an open matter
     Given the page
     And the page script
     Then Case file and History are not tabs
-    And My work offers Case file and History only while a matter is open
-    And they open on that matter, with My work still the marked tab
+    And an open matter offers Case file and History while it is open
+    And they open on that matter, with the matter's own tab still marked
   Scenario: The Legal library page says whether the library can be read
     Given the page
     Then the library availability line is on the Legal library page and not in the ribbon
@@ -2242,7 +2242,7 @@
       </c>
       <c r="G20" s="4" t="inlineStr">
         <is>
-          <t>Two lines: "Nyaymalaw is a legal research and matter workspace for advocates practising Telangana and Union of India law." and "Every answer shows the Act, section or judgment it rests on." Below them one button, Start a matter, which opens a new matter in My work. A sign-in lands on Home, except after a session that ended part-way through a brief, which goes straight back to that brief in My work.</t>
+          <t>Two lines: "Nyaymalaw is a legal research and matter workspace for advocates practising Telangana and Union of India law." and "Every answer shows the Act, section or judgment it rests on." Below them one button, Start a matter, which starts a new matter under Home (F-B-01). A sign-in lands on Home, except after a session that ended part-way through a brief, which goes straight back to that brief in My work.</t>
         </is>
       </c>
       <c r="H20" s="4" t="inlineStr">
@@ -2257,9 +2257,9 @@
     Then the home page says "Nyaymalaw is a legal research and matter workspace for advocates practising Telangana and Union of India law."
     And the home page says "Every answer shows the Act, section or judgment it rests on."
     And the home page has one button, "Start a matter", and nothing else
-  Scenario: Start a matter opens a new matter in My work
+  Scenario: Start a matter starts a new matter under Home
     Given the page script
-    Then the Start a matter button starts a new matter in My work
+    Then the Start a matter button starts a new matter under Home
   Scenario: A sign-in lands on Home unless a brief was interrupted
     Given the page script
     Then a sign-in shows the Home page
@@ -2314,7 +2314,20 @@
           <t>Route, triage, screen conflict, admit substance.</t>
         </is>
       </c>
-      <c r="C21" s="4" t="n"/>
+      <c r="C21" s="4" t="inlineStr">
+        <is>
+          <t>Stage 3 — Starting and resuming a matter (15 September 2026).
+When we click on Start a matter it should open a page within the Home tab. There it can start with New matter — The instruction — First, establish the brief. When we click on Record and continue it should open the chat. While this is happening the matters on the side should not be there; we should only see the plain New matter — First, establish the brief form. Once that form is submitted, we should open the chat. Once the chat is open and the first message is sent, the details required for the matter should be gathered from that first message, and then the matters dashboard pane should pop up. For new matters, just call it the matter board. This matter board should only have details regarding the current case. Whatever you have today — the X versus Y names, and below them client name, against, deadline, last worked, posture — keep them; we will add some more details that I will tell you.
+My work should only have the historical matters; it should not have the new matter establish-the-brief board. My work should only list all the matters, and when we click on a matter the matter board should shift left. The matter board is always on the left side across the tabs, both for a new matter and for My work's historical matters, and then you have the matter board and the matter chat window, similar to a new window. When we open a historical matter from My work it should open the matter with the matter board on the left side and the matter conversation, the chat window, on the right side — pretty much similar to a new matter. Basically we should be able to resume from where it was closed.
+To clarify: the matter board should be on the left side, with the small pane that we currently have, and the right side will be the chat window.
+Question 2, where the board's details come from: you are right. In the form we do share details like whom we are acting for and who is against, so immediately after the chat window opens, you can open the matter board and capture these details on it, and we can continue from there.
+Question 3, if the first message fails: from the subsequent messages we should gather more details, and whichever details are supposed to go to the matter board, the matter board can be updated accordingly. I will tell you which details need to go to the matter board in the subsequent messages.
+Question 4, where a new matter lives afterwards: as soon as a chat window opens and the matter board opens for a new matter, it should automatically create its own link in My work, which is the chat history. Even if we close the chat in between, we should be able to go to My work and resume it from there. With every message we should also update it. In fact, both of them — the new matter board and My work's historical board — should read the same database, so they are always in sync.
+Question 5, issues in this matter: yes, all the issues should go to the matter board.
+Question 6, My work: absolutely correct. My work should only be a list of past matters, and when a past matter is clicked it should again become the matter board and the chat, similar to a new matter, where the chat is resumable and the matter board is ready on the left side.
+I think we are good with all these details; just go ahead.</t>
+        </is>
+      </c>
       <c r="D21" s="4" t="n"/>
       <c r="E21" s="4" t="n"/>
       <c r="F21" s="4" t="n"/>
@@ -2330,121 +2343,370 @@
       <c r="P21" s="4" t="n"/>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>C. Take the brief</t>
-        </is>
-      </c>
-      <c r="B22" s="3" t="inlineStr">
-        <is>
-          <t>Account, objectives, parties, threads, chronology, material, evidence.</t>
-        </is>
-      </c>
-      <c r="C22" s="4" t="n"/>
-      <c r="D22" s="4" t="n"/>
-      <c r="E22" s="4" t="n"/>
-      <c r="F22" s="4" t="n"/>
-      <c r="G22" s="4" t="n"/>
-      <c r="H22" s="4" t="n"/>
-      <c r="I22" s="4" t="n"/>
-      <c r="J22" s="4" t="n"/>
-      <c r="K22" s="4" t="n"/>
-      <c r="L22" s="4" t="n"/>
-      <c r="M22" s="4" t="n"/>
-      <c r="N22" s="4" t="n"/>
-      <c r="O22" s="4" t="n"/>
-      <c r="P22" s="4" t="n"/>
+      <c r="A22" s="4" t="inlineStr">
+        <is>
+          <t>B. Open a matter</t>
+        </is>
+      </c>
+      <c r="B22" s="4" t="n"/>
+      <c r="C22" s="4" t="inlineStr">
+        <is>
+          <t>When we click on Start a matter it should open a page within the Home tab ... we should only see the plain New matter — First, establish the brief form. Once that form is submitted, we should open the chat. As soon as a chat window opens and the matter board opens for a new matter, it should automatically create its own link in My work, which is the chat history, so we can close it and resume it from there. Stage 4: as soon as a matter is created with the matter board and open chat, even if no message is sent, it should immediately be stored in the database and be visible in My work.</t>
+        </is>
+      </c>
+      <c r="D22" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E22" s="4" t="inlineStr">
+        <is>
+          <t>F-B-01</t>
+        </is>
+      </c>
+      <c r="F22" s="4" t="inlineStr">
+        <is>
+          <t>Start a new matter from Home</t>
+        </is>
+      </c>
+      <c r="G22" s="4" t="inlineStr">
+        <is>
+          <t>Start a matter, on Home, opens the intake form alone — no list of other matters and no board — with Home still the marked tab. Record and continue saves the matter on the server with the parties the form gave, named from them (X v Y); only when the server confirms it is saved do the chat and the matter board open, and from that moment the matter is in My work's list.</t>
+        </is>
+      </c>
+      <c r="H22" s="4" t="inlineStr">
+        <is>
+          <t>Show other matters or a board before the matter is saved; open a chat for a matter the server has not confirmed; lose the form's answers when the matter cannot be opened; open a second matter when a lost response is retried.</t>
+        </is>
+      </c>
+      <c r="I22" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: Start a matter opens the intake form alone, under Home
+    Given the page script
+    And the page stylesheet
+    Then Start a matter opens the intake form alone, with Home still the marked tab
+  Scenario: Record and continue saves the matter before the chat opens
+    Given the page script
+    Then recording the intake saves the matter on the server with the form's parties before the chat opens
+    And if the matter cannot be opened the form keeps its answers and says so
+  Scenario: The server names a new matter from its parties and lists it at once
+    When an advocate opens a matter for "Ramesh Traders" against "Kiran Steels" without a title
+    Then the matter is saved as "Ramesh Traders v Kiran Steels" with both parties recorded
+    And it is in My work's list straight away
+</t>
+        </is>
+      </c>
+      <c r="J22" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/open_a_matter/F-B-01.feature (3 scenarios).</t>
+        </is>
+      </c>
+      <c r="K22" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L22" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; the browser journeys pass.</t>
+        </is>
+      </c>
+      <c r="M22" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O22" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). The browser journeys were updated to start matters from Home and to My work's list, and have not been run.</t>
+        </is>
+      </c>
+      <c r="P22" s="4" t="inlineStr">
+        <is>
+          <t>The scope and capacity answers still travel with the first brief, where the intake screens run before any fact is admitted (BK-34). Confirmed 15 September 2026: a matter saved with no message sent is listed in My work (a direct check on the store). The error the product owner saw came from a server started before this change, since restarted.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>D. Work the file</t>
-        </is>
-      </c>
-      <c r="B23" s="3" t="inlineStr">
-        <is>
-          <t>Cause, limitation, forum, jurisdiction, deadlines, research, proof, theory.</t>
-        </is>
-      </c>
-      <c r="C23" s="4" t="n"/>
-      <c r="D23" s="4" t="n"/>
-      <c r="E23" s="4" t="n"/>
-      <c r="F23" s="4" t="n"/>
-      <c r="G23" s="4" t="n"/>
-      <c r="H23" s="4" t="n"/>
-      <c r="I23" s="4" t="n"/>
-      <c r="J23" s="4" t="n"/>
-      <c r="K23" s="4" t="n"/>
-      <c r="L23" s="4" t="n"/>
-      <c r="M23" s="4" t="n"/>
-      <c r="N23" s="4" t="n"/>
-      <c r="O23" s="4" t="n"/>
-      <c r="P23" s="4" t="n"/>
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>B. Open a matter</t>
+        </is>
+      </c>
+      <c r="B23" s="4" t="n"/>
+      <c r="C23" s="4" t="inlineStr">
+        <is>
+          <t>For new matters, just call it the matter board. This matter board should only have details regarding the current case: the X versus Y names, and below them client name, against, deadline, last worked, posture — keep them; we will add more. The matter board should be on the left side, with the small pane that we currently have, and the right side will be the chat window. All the issues should go to the matter board. Both the new matter board and My work's historical board should read the same database, so they are always in sync.</t>
+        </is>
+      </c>
+      <c r="D23" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E23" s="4" t="inlineStr">
+        <is>
+          <t>F-B-02</t>
+        </is>
+      </c>
+      <c r="F23" s="4" t="inlineStr">
+        <is>
+          <t>The matter board beside the chat</t>
+        </is>
+      </c>
+      <c r="G23" s="4" t="inlineStr">
+        <is>
+          <t>In an open matter the matter board is the left pane and the chat the right, whether the matter was started from Home or opened from My work. The board shows this matter only: its X v Y name, client, against, deadline, last worked and posture, then the issues recorded on the matter. It is read from the same record My work lists and read again after every message, so what later messages add reaches it.</t>
+        </is>
+      </c>
+      <c r="H23" s="4" t="inlineStr">
+        <is>
+          <t>Show another matter's details; be put together from anything but the saved record; show an unreadable board as an empty one.</t>
+        </is>
+      </c>
+      <c r="I23" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The matter board is on the left and the chat on the right
+    Given the page
+    And the page stylesheet
+    Then in an open matter the board is the left pane and the chat the right
+  Scenario: The board shows this matter only, from the record My work lists
+    Given the page script
+    Then the board is filled from My work's row for this matter, with the same fields as the list
+    And the board is read again after every message
+    And a board that cannot be read says so rather than showing an empty one
+  Scenario: The issues in the matter are on the board
+    Given the page
+    And the page script
+    Then the issues recorded on the matter are listed on the board under its details
+</t>
+        </is>
+      </c>
+      <c r="J23" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/open_a_matter/F-B-02.feature (3 scenarios).</t>
+        </is>
+      </c>
+      <c r="K23" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L23" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; the browser journeys pass.</t>
+        </is>
+      </c>
+      <c r="M23" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O23" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). The browser journeys were updated to start matters from Home and to My work's list, and have not been run.</t>
+        </is>
+      </c>
+      <c r="P23" s="4" t="inlineStr">
+        <is>
+          <t>More board fields to come from the product owner. On a phone the board opens from the Matter board button above the chat.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>E. Advise</t>
-        </is>
-      </c>
-      <c r="B24" s="3" t="inlineStr">
-        <is>
-          <t>Scenarios, recommendation, proportionality, decision, disagreement.</t>
-        </is>
-      </c>
-      <c r="C24" s="4" t="n"/>
-      <c r="D24" s="4" t="n"/>
-      <c r="E24" s="4" t="n"/>
-      <c r="F24" s="4" t="n"/>
-      <c r="G24" s="4" t="n"/>
-      <c r="H24" s="4" t="n"/>
-      <c r="I24" s="4" t="n"/>
-      <c r="J24" s="4" t="n"/>
-      <c r="K24" s="4" t="n"/>
-      <c r="L24" s="4" t="n"/>
-      <c r="M24" s="4" t="n"/>
-      <c r="N24" s="4" t="n"/>
-      <c r="O24" s="4" t="n"/>
-      <c r="P24" s="4" t="n"/>
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>B. Open a matter</t>
+        </is>
+      </c>
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="inlineStr">
+        <is>
+          <t>My work should only have the historical matters; it should only list all the matters. When we open a historical matter from My work it should open with the matter board on the left side and the chat window on the right side — pretty much similar to a new matter. Basically we should be able to resume from where it was closed.</t>
+        </is>
+      </c>
+      <c r="D24" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E24" s="4" t="inlineStr">
+        <is>
+          <t>F-B-03</t>
+        </is>
+      </c>
+      <c r="F24" s="4" t="inlineStr">
+        <is>
+          <t>My work lists the matters, and opening one resumes it</t>
+        </is>
+      </c>
+      <c r="G24" s="4" t="inlineStr">
+        <is>
+          <t>My work is only the list of matters: no new-matter button and no welcome page, and choosing the My work tab always shows the list. Opening a matter shows its board on the left and restores its conversation on the right, with My work still the marked tab. A matter started from Home is resumed from here the same way.</t>
+        </is>
+      </c>
+      <c r="H24" s="4" t="inlineStr">
+        <is>
+          <t>Offer a way to start a matter from My work; open a matter without its saved conversation; move a matter opened from My work under another tab.</t>
+        </is>
+      </c>
+      <c r="I24" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: My work is only the list of matters
+    Given the page
+    And the page script
+    And the page stylesheet
+    Then My work has no new-matter button and no welcome page
+    And choosing the My work tab always shows the list of matters
+  Scenario: Opening a matter from My work resumes it
+    Given the page script
+    Then opening a matter shows its board and restores its conversation, with My work still the marked tab
+</t>
+        </is>
+      </c>
+      <c r="J24" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/open_a_matter/F-B-03.feature (2 scenarios).</t>
+        </is>
+      </c>
+      <c r="K24" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L24" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; the browser journeys pass.</t>
+        </is>
+      </c>
+      <c r="M24" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O24" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead). The browser journeys were updated to start matters from Home and to My work's list, and have not been run.</t>
+        </is>
+      </c>
+      <c r="P24" s="4" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>F. Act</t>
-        </is>
-      </c>
-      <c r="B25" s="3" t="inlineStr">
-        <is>
-          <t>Negotiate, brief the drafter, draft, file, witnesses, hearing, court.</t>
-        </is>
-      </c>
-      <c r="C25" s="4" t="n"/>
-      <c r="D25" s="4" t="n"/>
-      <c r="E25" s="4" t="n"/>
-      <c r="F25" s="4" t="n"/>
-      <c r="G25" s="4" t="n"/>
-      <c r="H25" s="4" t="n"/>
-      <c r="I25" s="4" t="n"/>
-      <c r="J25" s="4" t="n"/>
-      <c r="K25" s="4" t="n"/>
-      <c r="L25" s="4" t="n"/>
-      <c r="M25" s="4" t="n"/>
-      <c r="N25" s="4" t="n"/>
-      <c r="O25" s="4" t="n"/>
-      <c r="P25" s="4" t="n"/>
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>B. Open a matter</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>Remove this [the bar with Matter cover &amp; instructions, Attributed file and Protective handoff]. Decision: I'm okay with what you propose — move them into the matter's header beside Case file and History.</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>F-B-04</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>The matter's own tools sit in its header</t>
+        </is>
+      </c>
+      <c r="G25" s="4" t="inlineStr">
+        <is>
+          <t>Matter cover &amp; instructions, Attributed file and Protective handoff are in the open matter's header, beside Case file and History, instead of a bar above the chat.</t>
+        </is>
+      </c>
+      <c r="H25" s="4" t="inlineStr">
+        <is>
+          <t>Drop any of the three; put Protective handoff more than one click away in an open matter.</t>
+        </is>
+      </c>
+      <c r="I25" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The matter's own tools sit in its header
+    Given the page script
+    Then Matter cover &amp; instructions, Attributed file and Protective handoff sit in the matter's header beside Case file and History
+</t>
+        </is>
+      </c>
+      <c r="J25" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/open_a_matter/F-B-04.feature (1 scenario).</t>
+        </is>
+      </c>
+      <c r="K25" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L25" s="4" t="inlineStr">
+        <is>
+          <t>The scenario passes; the browser journeys pass.</t>
+        </is>
+      </c>
+      <c r="M25" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O25" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead).</t>
+        </is>
+      </c>
+      <c r="P25" s="4" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>G. Carry</t>
+          <t>C. Take the brief</t>
         </is>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>Proactive service, conflict watch, handover.</t>
-        </is>
-      </c>
-      <c r="C26" s="4" t="n"/>
+          <t>Account, objectives, parties, threads, chronology, material, evidence.</t>
+        </is>
+      </c>
+      <c r="C26" s="4" t="inlineStr">
+        <is>
+          <t>Stage 4 — Adding material and dictating (15 September 2026).
+Remove this [the "Add files or record a voice note" bar, and the bar with Matter cover &amp; instructions, Attributed file and Protective handoff]. Put a plus button just below the text box; it should have options to upload files and multimedia. Beside the plus, put a mic button to record audio and turn it into text instead of typing every time. Also, as soon as a matter is created with the matter board and open chat, even if no message is sent, it should immediately be stored in the database and be visible in My work, the chat history.
+Decisions: I'm okay with one and two and what you propose [the three matter tools move into the matter's header beside Case file and History; the plus menu offers Upload documents, Upload photos, audio or video, and Record a voice note to keep]. For the third, how the mic turns speech into text, we should go with our own server, a local one. I have an 8 GB GPU on this laptop, so with that context, if you think you can use a better open source model, do that.
+Decision (15 September 2026): install v3 large then.
+Follow-up (15 September 2026): transcribing to Urdu/Arabic — it should be English.
+Stage 5 — Live dictation (15 September 2026).
+I want the transcription to be live and instant word by word, instead of recording the complete message and then transcribing.
+Questions: is option C also open source? Can it run smoothly on my 8 GB GPU? Does it understand Indian English well?
+Decision: build the Vosk live plus Whisper final version.</t>
+        </is>
+      </c>
       <c r="D26" s="4" t="n"/>
       <c r="E26" s="4" t="n"/>
       <c r="F26" s="4" t="n"/>
@@ -2460,59 +2722,438 @@
       <c r="P26" s="4" t="n"/>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
+      <c r="A27" s="4" t="inlineStr">
+        <is>
+          <t>C. Take the brief</t>
+        </is>
+      </c>
+      <c r="B27" s="4" t="n"/>
+      <c r="C27" s="4" t="inlineStr">
+        <is>
+          <t>Put a plus button just below the text box; it should have options to upload files and multimedia. Remove the "Add files or record a voice note" bar. Decision: the plus menu as proposed.</t>
+        </is>
+      </c>
+      <c r="D27" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E27" s="4" t="inlineStr">
+        <is>
+          <t>F-C-01</t>
+        </is>
+      </c>
+      <c r="F27" s="4" t="inlineStr">
+        <is>
+          <t>Add documents, media or a voice note from the plus button</t>
+        </is>
+      </c>
+      <c r="G27" s="4" t="inlineStr">
+        <is>
+          <t>A plus button just under the brief opens a small menu: Upload documents, Upload photos, audio or video, and Record a voice note to keep. Each opens the original-material window, which keeps what it receives sealed and unread. There is no files bar above the chat.</t>
+        </is>
+      </c>
+      <c r="H27" s="4" t="inlineStr">
+        <is>
+          <t>Read, transcribe or admit an uploaded file as a fact; leave the old files bar in place.</t>
+        </is>
+      </c>
+      <c r="I27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: A plus button under the brief offers documents, media and a voice note to keep
+    Given the page
+    And the page script
+    Then under the brief a plus button opens Upload documents, Upload photos, audio or video, and Record a voice note to keep
+    And each opens the original-material window, which keeps what it receives sealed and unread
+    And there is no files bar above the chat
+</t>
+        </is>
+      </c>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/take_the_brief/F-C-01.feature (1 scenario).</t>
+        </is>
+      </c>
+      <c r="K27" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L27" s="4" t="inlineStr">
+        <is>
+          <t>The scenario passes; the upload browser journey passes.</t>
+        </is>
+      </c>
+      <c r="M27" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O27" s="4" t="inlineStr">
+        <is>
+          <t>Not run: the scenarios are written and have not been run (runs need your go-ahead).</t>
+        </is>
+      </c>
+      <c r="P27" s="4" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="4" t="inlineStr">
+        <is>
+          <t>C. Take the brief</t>
+        </is>
+      </c>
+      <c r="B28" s="4" t="n"/>
+      <c r="C28" s="4" t="inlineStr">
+        <is>
+          <t>Beside the plus, put a mic button to record audio and turn it into text instead of typing every time. Decision: our own server, a local one. I have an 8 GB GPU on this laptop; if you think you can use a better open source model, do that. Decision, 15 September 2026: install v3 large then. Follow-up, 15 September 2026: transcribing to Urdu/Arabic — it should be English.</t>
+        </is>
+      </c>
+      <c r="D28" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E28" s="4" t="inlineStr">
+        <is>
+          <t>F-C-02</t>
+        </is>
+      </c>
+      <c r="F28" s="4" t="inlineStr">
+        <is>
+          <t>Dictate the brief with the mic, transcribed on this installation</t>
+        </is>
+      </c>
+      <c r="G28" s="4" t="inlineStr">
+        <is>
+          <t>A mic button beside the plus records while pressed on and stops on a second press. The recording is transcribed by an open-source Whisper model (large-v3) running on this installation, on the GPU where it can; the words come back into the brief box at the cursor to be checked and edited, in English. Nothing is sent by itself, and the recording is not kept. If the speech model is not set up, the mic says so.</t>
+        </is>
+      </c>
+      <c r="H28" s="4" t="inlineStr">
+        <is>
+          <t>Send the recording to any outside service; keep the recording; send the brief without the advocate pressing Send; return empty text when the model could not run. Leave the language to detection, which on a few seconds of Indian-accented English returns a script the advocate cannot read.</t>
+        </is>
+      </c>
+      <c r="I28" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The mic sits beside the plus and puts what was said into the brief for checking
+    Given the page
+    And the page script
+    Then beside the plus button there is a mic button that starts recording and stops on a second press
+    And the words come back into the brief box to be checked, and nothing is sent by itself
+  Scenario: Speech is turned into text on this installation and the recording is not kept
+    Given the dictation service
+    When an advocate sends a short recording to be transcribed
+    Then the words come back and the recording is not stored anywhere
+    And it went through the recorded local speech processor
+  Scenario: Dictation that is not set up says so
+    When the local speech model is not installed and an advocate dictates
+    Then dictation is refused, saying the local speech model is not installed
+  Scenario: The words come back in English
+    Then dictation asks the speech model for English unless the installation sets another language
+</t>
+        </is>
+      </c>
+      <c r="J28" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/take_the_brief/F-C-02.feature (4 scenarios).</t>
+        </is>
+      </c>
+      <c r="K28" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L28" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; a real dictation in the browser comes back as text.</t>
+        </is>
+      </c>
+      <c r="M28" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O28" s="4" t="inlineStr">
+        <is>
+          <t>Installed 15 Sep 2026: faster-whisper 1.2.1 (with ctranslate2 4.8.2 and av 18.1.0) and the Whisper large-v3 model (2.9 GB in .nm/models). Measured on the RTX 4060 through the product's own adapter: a 13.6-second spoken test clip (Windows synthetic voice, English) transcribed in 1.9 s cold and 1.4 s warm, word for word. Not run: the scenarios are written and have not been run (runs need your go-ahead). Not yet tried with a real voice in the browser. Fixed 15 Sep 2026 after the product owner's first real dictation came back in Urdu script: the model is now asked for English, and the same words ("Hi, I am Rahul") come back in English through the product's adapter.</t>
+        </is>
+      </c>
+      <c r="P28" s="4" t="inlineStr">
+        <is>
+          <t>The GPU libraries come from the installed PyTorch; the adapter puts them on PATH (the first attempt failed with "cublas64_12.dll is not found" until it did). NM_DICTATION_MODEL=large-v3-turbo is faster and slightly less accurate. Dictation asks for English (NM_DICTATION_LANGUAGE=auto detects the language instead, and NM_DICTATION_TRANSLATE=1 with it brings other languages back in English). Not yet measured: Hindi, Telugu and mixed speech, and real microphone audio. Recorded as the in-process processor local-speech. The words appearing while you speak are F-C-03; this row is the accurate transcription that replaces them.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="4" t="inlineStr">
+        <is>
+          <t>C. Take the brief</t>
+        </is>
+      </c>
+      <c r="B29" s="4" t="n"/>
+      <c r="C29" s="4" t="inlineStr">
+        <is>
+          <t>I want the transcription to be live and instant word by word, instead of recording the complete message and then transcribing. Decision, 15 September 2026: build the Vosk live plus Whisper final version.</t>
+        </is>
+      </c>
+      <c r="D29" s="4" t="inlineStr">
+        <is>
+          <t>Feature</t>
+        </is>
+      </c>
+      <c r="E29" s="4" t="inlineStr">
+        <is>
+          <t>F-C-03</t>
+        </is>
+      </c>
+      <c r="F29" s="4" t="inlineStr">
+        <is>
+          <t>Live words while the advocate speaks</t>
+        </is>
+      </c>
+      <c r="G29" s="4" t="inlineStr">
+        <is>
+          <t>While the mic is on, the words appear in the brief box as they are spoken, from a small Indian-English model running on this machine's processor (Vosk), over a socket that authenticates itself and checks the page's origin. They are provisional: the accurate transcription from Whisper large-v3 replaces them when the advocate stops. If the advocate edits the live words, the live words let go rather than overwrite the edit, and say so. Live words being unavailable never stops the recording or the final transcription.</t>
+        </is>
+      </c>
+      <c r="H29" s="4" t="inlineStr">
+        <is>
+          <t>Send the audio to any outside service; keep the audio; overwrite the advocate's own edits; play their own voice back at them; run the socket without a signed-in session and a same-origin handshake; let the provisional words be the text that is kept.</t>
+        </is>
+      </c>
+      <c r="I29" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">  Scenario: The words appear in the brief box as they are spoken
+    Given the page
+    And the page script
+    Then the live words come from a socket and are written into the brief box as they arrive
+    And the live words stop being written the moment the advocate edits them
+    And the final transcription replaces the live words it stood in for
+  Scenario: The microphone reaches the live model as it wants it, and not the speakers
+    Given the page script
+    Then the audio is sent as 16 kHz mono frames of about a tenth of a second
+    And the page does not play the advocate's own voice back
+  Scenario: The live socket authenticates itself
+    When a stranger opens the live dictation socket
+    Then the socket is refused before any audio is read
+    And a socket opened from another page is refused the same way
+  Scenario: The live words arrive while the advocate is still speaking
+    Given the live dictation service
+    When the page sends two frames of speech and then stops
+    Then the words heard so far come back after each frame
+    And the final words come back when it stops
+    And no audio is stored anywhere
+  Scenario: Live words that are not set up do not stop the dictation
+    Given the page script
+    When the live speech model is not downloaded and an advocate dictates
+    Then the socket says the live words are off and the recording goes on
+</t>
+        </is>
+      </c>
+      <c r="J29" s="4" t="inlineStr">
+        <is>
+          <t>tests/features/take_the_brief/F-C-03.feature (5 scenarios).</t>
+        </is>
+      </c>
+      <c r="K29" s="4" t="inlineStr">
+        <is>
+          <t>Offline test</t>
+        </is>
+      </c>
+      <c r="L29" s="4" t="inlineStr">
+        <is>
+          <t>All scenarios pass; in the browser the words appear while speaking and the final transcription replaces them.</t>
+        </is>
+      </c>
+      <c r="M29" s="4" t="inlineStr">
+        <is>
+          <t>Pilot</t>
+        </is>
+      </c>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>Built</t>
+        </is>
+      </c>
+      <c r="O29" s="4" t="inlineStr">
+        <is>
+          <t>MEASURED 18 September 2026, with the live model installed. Words arrive while the sentence is still being spoken: on a 7.6s clip the first words showed at 0.9s and the line was revised 21 times before the speaker stopped. Cost on the processor: mean 18 ms per 100 ms frame, median 0 ms, 2 of 76 frames slower than the audio they carry (142 ms, 243 ms, where the recogniser settles a phrase), 1.35s of processor time for 7.6s of speech. The live words are rough -- 'in the district court and hyderabad', no punctuation -- and Whisper large-v3 replaced them with 'The plaintiff filed a suit for specific performance in the district court at Hyderabad, and the defendant denies the agreement.' All 5 scenarios pass, and the socket refuses a stranger and a foreign origin with 403 before reading any audio. NOT YET MEASURED: a real voice at the microphone, and accents other than the synthesised clip's.</t>
+        </is>
+      </c>
+      <c r="P29" s="4" t="inlineStr">
+        <is>
+          <t>Setup, two steps: `python -m pip install vosk --no-deps`, then `SETUPTOOLS_USE_DISTUTILS=stdlib python -m pip install srt` (srt ships no wheel, so it builds, and this machine's setuptools `_distutils_hack` aborts every sdist build without that variable -- measured 18 September 2026). THE --no-deps IS BECAUSE srt HAS NO WHEEL HERE AND srt IS STILL REQUIRED: I first noted that srt was only used by vosk's command-line tool, and that was wrong -- `vosk/__init__.py` imports it at package import, so vosk installed without it cannot be imported at all. Measured 18 September 2026 (B-143): health reported the live words as ready and the first frame of speech failed. The model is fetched by `python development_environment/developer_tooling/get_live_speech_model.py` into .nm/models; NM_DICTATION_LIVE_MODEL names another folder. Whisper large-v3 still produces the text that is kept, so the live model's rougher words never reach the file.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>D. Work the file</t>
+        </is>
+      </c>
+      <c r="B30" s="3" t="inlineStr">
+        <is>
+          <t>Cause, limitation, forum, jurisdiction, deadlines, research, proof, theory.</t>
+        </is>
+      </c>
+      <c r="C30" s="4" t="n"/>
+      <c r="D30" s="4" t="n"/>
+      <c r="E30" s="4" t="n"/>
+      <c r="F30" s="4" t="n"/>
+      <c r="G30" s="4" t="n"/>
+      <c r="H30" s="4" t="n"/>
+      <c r="I30" s="4" t="n"/>
+      <c r="J30" s="4" t="n"/>
+      <c r="K30" s="4" t="n"/>
+      <c r="L30" s="4" t="n"/>
+      <c r="M30" s="4" t="n"/>
+      <c r="N30" s="4" t="n"/>
+      <c r="O30" s="4" t="n"/>
+      <c r="P30" s="4" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>E. Advise</t>
+        </is>
+      </c>
+      <c r="B31" s="3" t="inlineStr">
+        <is>
+          <t>Scenarios, recommendation, proportionality, decision, disagreement.</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="n"/>
+      <c r="D31" s="4" t="n"/>
+      <c r="E31" s="4" t="n"/>
+      <c r="F31" s="4" t="n"/>
+      <c r="G31" s="4" t="n"/>
+      <c r="H31" s="4" t="n"/>
+      <c r="I31" s="4" t="n"/>
+      <c r="J31" s="4" t="n"/>
+      <c r="K31" s="4" t="n"/>
+      <c r="L31" s="4" t="n"/>
+      <c r="M31" s="4" t="n"/>
+      <c r="N31" s="4" t="n"/>
+      <c r="O31" s="4" t="n"/>
+      <c r="P31" s="4" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>F. Act</t>
+        </is>
+      </c>
+      <c r="B32" s="3" t="inlineStr">
+        <is>
+          <t>Negotiate, brief the drafter, draft, file, witnesses, hearing, court.</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+      <c r="G32" s="4" t="n"/>
+      <c r="H32" s="4" t="n"/>
+      <c r="I32" s="4" t="n"/>
+      <c r="J32" s="4" t="n"/>
+      <c r="K32" s="4" t="n"/>
+      <c r="L32" s="4" t="n"/>
+      <c r="M32" s="4" t="n"/>
+      <c r="N32" s="4" t="n"/>
+      <c r="O32" s="4" t="n"/>
+      <c r="P32" s="4" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>G. Carry</t>
+        </is>
+      </c>
+      <c r="B33" s="3" t="inlineStr">
+        <is>
+          <t>Proactive service, conflict watch, handover.</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="n"/>
+      <c r="D33" s="4" t="n"/>
+      <c r="E33" s="4" t="n"/>
+      <c r="F33" s="4" t="n"/>
+      <c r="G33" s="4" t="n"/>
+      <c r="H33" s="4" t="n"/>
+      <c r="I33" s="4" t="n"/>
+      <c r="J33" s="4" t="n"/>
+      <c r="K33" s="4" t="n"/>
+      <c r="L33" s="4" t="n"/>
+      <c r="M33" s="4" t="n"/>
+      <c r="N33" s="4" t="n"/>
+      <c r="O33" s="4" t="n"/>
+      <c r="P33" s="4" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
         <is>
           <t>H. Close</t>
         </is>
       </c>
-      <c r="B27" s="3" t="inlineStr">
+      <c r="B34" s="3" t="inlineStr">
         <is>
           <t>Capture events, close and reopen.</t>
         </is>
       </c>
-      <c r="C27" s="4" t="n"/>
-      <c r="D27" s="4" t="n"/>
-      <c r="E27" s="4" t="n"/>
-      <c r="F27" s="4" t="n"/>
-      <c r="G27" s="4" t="n"/>
-      <c r="H27" s="4" t="n"/>
-      <c r="I27" s="4" t="n"/>
-      <c r="J27" s="4" t="n"/>
-      <c r="K27" s="4" t="n"/>
-      <c r="L27" s="4" t="n"/>
-      <c r="M27" s="4" t="n"/>
-      <c r="N27" s="4" t="n"/>
-      <c r="O27" s="4" t="n"/>
-      <c r="P27" s="4" t="n"/>
-    </row>
-    <row r="28">
-      <c r="A28" s="2" t="inlineStr">
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+      <c r="G34" s="4" t="n"/>
+      <c r="H34" s="4" t="n"/>
+      <c r="I34" s="4" t="n"/>
+      <c r="J34" s="4" t="n"/>
+      <c r="K34" s="4" t="n"/>
+      <c r="L34" s="4" t="n"/>
+      <c r="M34" s="4" t="n"/>
+      <c r="N34" s="4" t="n"/>
+      <c r="O34" s="4" t="n"/>
+      <c r="P34" s="4" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
         <is>
           <t>I. Leave</t>
         </is>
       </c>
-      <c r="B28" s="3" t="inlineStr">
+      <c r="B35" s="3" t="inlineStr">
         <is>
           <t>End the session and leave nothing behind.</t>
         </is>
       </c>
-      <c r="C28" s="4" t="n"/>
-      <c r="D28" s="4" t="n"/>
-      <c r="E28" s="4" t="n"/>
-      <c r="F28" s="4" t="n"/>
-      <c r="G28" s="4" t="n"/>
-      <c r="H28" s="4" t="n"/>
-      <c r="I28" s="4" t="n"/>
-      <c r="J28" s="4" t="n"/>
-      <c r="K28" s="4" t="n"/>
-      <c r="L28" s="4" t="n"/>
-      <c r="M28" s="4" t="n"/>
-      <c r="N28" s="4" t="n"/>
-      <c r="O28" s="4" t="n"/>
-      <c r="P28" s="4" t="n"/>
+      <c r="C35" s="4" t="n"/>
+      <c r="D35" s="4" t="n"/>
+      <c r="E35" s="4" t="n"/>
+      <c r="F35" s="4" t="n"/>
+      <c r="G35" s="4" t="n"/>
+      <c r="H35" s="4" t="n"/>
+      <c r="I35" s="4" t="n"/>
+      <c r="J35" s="4" t="n"/>
+      <c r="K35" s="4" t="n"/>
+      <c r="L35" s="4" t="n"/>
+      <c r="M35" s="4" t="n"/>
+      <c r="N35" s="4" t="n"/>
+      <c r="O35" s="4" t="n"/>
+      <c r="P35" s="4" t="n"/>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P28"/>
+  <autoFilter ref="A1:P34"/>
   <dataValidations count="4">
     <dataValidation sqref="D2:D500" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Feature,Phase gate,Whole journey"</formula1>
